--- a/research/traditional_assets/database/data/turkey/turkey_restaurant_dining.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_restaurant_dining.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="ibse_etilr" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,28 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.195</v>
-      </c>
-      <c r="E2">
-        <v>0.289</v>
+        <v>0.877</v>
       </c>
       <c r="G2">
-        <v>0.1664392905866303</v>
+        <v>0.07387820512820513</v>
       </c>
       <c r="H2">
-        <v>0.1664392905866303</v>
+        <v>0.07387820512820513</v>
       </c>
       <c r="I2">
-        <v>0.02319236016371078</v>
+        <v>0.1299679487179487</v>
       </c>
       <c r="J2">
-        <v>0.01856510571750488</v>
+        <v>0.1269629094412331</v>
       </c>
       <c r="K2">
-        <v>0.662</v>
+        <v>1.69</v>
       </c>
       <c r="L2">
-        <v>0.9031377899045021</v>
+        <v>0.2708333333333333</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,70 +632,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.15</v>
+        <v>0.771</v>
       </c>
       <c r="V2">
-        <v>0.1666666666666667</v>
+        <v>0.0260472972972973</v>
       </c>
       <c r="W2">
-        <v>0.249811320754717</v>
+        <v>0.3755555555555555</v>
       </c>
       <c r="X2">
-        <v>0.1106830006931517</v>
+        <v>0.189071709532898</v>
       </c>
       <c r="Y2">
-        <v>0.1391283200615653</v>
+        <v>0.1864838460226576</v>
       </c>
       <c r="Z2">
-        <v>1.527083333333334</v>
+        <v>4.716553287981858</v>
       </c>
       <c r="AA2">
-        <v>0.02835046352277308</v>
+        <v>0.5988273279767911</v>
       </c>
       <c r="AB2">
-        <v>0.1106238763514458</v>
+        <v>0.1834589197238851</v>
       </c>
       <c r="AC2">
-        <v>-0.0822734128286727</v>
+        <v>0.415368408252906</v>
       </c>
       <c r="AD2">
-        <v>0.022</v>
+        <v>2.08</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.022</v>
+        <v>2.08</v>
       </c>
       <c r="AG2">
-        <v>-3.128</v>
+        <v>1.309</v>
       </c>
       <c r="AH2">
-        <v>0.001162667794102104</v>
+        <v>0.06565656565656566</v>
       </c>
       <c r="AI2">
-        <v>0.004865103936311366</v>
+        <v>0.3501683501683502</v>
       </c>
       <c r="AJ2">
-        <v>-0.1983261476033477</v>
+        <v>0.04235012455918988</v>
       </c>
       <c r="AK2">
-        <v>-2.279883381924198</v>
+        <v>0.253240472044883</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="AM2">
-        <v>-0.87</v>
+        <v>-0.179</v>
       </c>
       <c r="AN2">
-        <v>0.4680851063829787</v>
+        <v>2.399077277970012</v>
+      </c>
+      <c r="AO2">
+        <v>17.25531914893617</v>
       </c>
       <c r="AP2">
-        <v>-66.55319148936171</v>
+        <v>1.509803921568628</v>
       </c>
       <c r="AQ2">
-        <v>-0.01954022988505747</v>
+        <v>-4.53072625698324</v>
       </c>
     </row>
     <row r="3">
@@ -716,28 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.195</v>
-      </c>
-      <c r="E3">
-        <v>0.289</v>
+        <v>0.877</v>
       </c>
       <c r="G3">
-        <v>0.1664392905866303</v>
+        <v>0.07387820512820513</v>
       </c>
       <c r="H3">
-        <v>0.1664392905866303</v>
+        <v>0.07387820512820513</v>
       </c>
       <c r="I3">
-        <v>0.02319236016371078</v>
+        <v>0.1299679487179487</v>
       </c>
       <c r="J3">
-        <v>0.01856510571750488</v>
+        <v>0.1269629094412331</v>
       </c>
       <c r="K3">
-        <v>0.662</v>
+        <v>1.69</v>
       </c>
       <c r="L3">
-        <v>0.9031377899045021</v>
+        <v>0.2708333333333333</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -761,70 +760,8785 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.15</v>
+        <v>0.771</v>
       </c>
       <c r="V3">
-        <v>0.1666666666666667</v>
+        <v>0.0260472972972973</v>
       </c>
       <c r="W3">
-        <v>0.249811320754717</v>
+        <v>0.3755555555555555</v>
       </c>
       <c r="X3">
-        <v>0.1106830006931517</v>
+        <v>0.189071709532898</v>
       </c>
       <c r="Y3">
-        <v>0.1391283200615653</v>
+        <v>0.1864838460226576</v>
       </c>
       <c r="Z3">
-        <v>1.527083333333334</v>
+        <v>4.716553287981858</v>
       </c>
       <c r="AA3">
-        <v>0.02835046352277308</v>
+        <v>0.5988273279767911</v>
       </c>
       <c r="AB3">
-        <v>0.1106238763514458</v>
+        <v>0.1834589197238851</v>
       </c>
       <c r="AC3">
-        <v>-0.0822734128286727</v>
+        <v>0.415368408252906</v>
       </c>
       <c r="AD3">
-        <v>0.022</v>
+        <v>2.08</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.022</v>
+        <v>2.08</v>
       </c>
       <c r="AG3">
-        <v>-3.128</v>
+        <v>1.309</v>
       </c>
       <c r="AH3">
-        <v>0.001162667794102104</v>
+        <v>0.06565656565656566</v>
       </c>
       <c r="AI3">
-        <v>0.004865103936311366</v>
+        <v>0.3501683501683502</v>
       </c>
       <c r="AJ3">
-        <v>-0.1983261476033477</v>
+        <v>0.04235012455918988</v>
       </c>
       <c r="AK3">
-        <v>-2.279883381924198</v>
+        <v>0.253240472044883</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="AM3">
-        <v>-0.87</v>
+        <v>-0.179</v>
       </c>
       <c r="AN3">
-        <v>0.4680851063829787</v>
+        <v>2.399077277970012</v>
+      </c>
+      <c r="AO3">
+        <v>17.25531914893617</v>
       </c>
       <c r="AP3">
-        <v>-66.55319148936171</v>
+        <v>1.509803921568628</v>
       </c>
       <c r="AQ3">
-        <v>-0.01954022988505747</v>
+        <v>-4.53072625698324</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Etiler Gida Ve Ticari Yatirimlar Sanayi Ve Ticaret Anonim Sirketi (IBSE:ETILR)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IBSE:ETILR</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Restaurant/Dining</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0656565656565657</v>
+      </c>
+      <c r="F2">
+        <v>0.1</v>
+      </c>
+      <c r="G2">
+        <v>29.6</v>
+      </c>
+      <c r="H2">
+        <v>29.6242291545473</v>
+      </c>
+      <c r="I2">
+        <v>30.909</v>
+      </c>
+      <c r="J2">
+        <v>32.0212291545473</v>
+      </c>
+      <c r="K2">
+        <v>2.08</v>
+      </c>
+      <c r="L2">
+        <v>3.168</v>
+      </c>
+      <c r="M2">
+        <v>0.183458919723885</v>
+      </c>
+      <c r="N2">
+        <v>0.178434319724751</v>
+      </c>
+      <c r="O2">
+        <v>0.103584603211009</v>
+      </c>
+      <c r="P2">
+        <v>0.04235</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.189071709532898</v>
+      </c>
+      <c r="T2">
+        <v>0.193554799694168</v>
+      </c>
+      <c r="U2">
+        <v>0.877125281413919</v>
+      </c>
+      <c r="V2">
+        <v>0.903292759853676</v>
+      </c>
+      <c r="W2">
+        <v>4.654499540863177</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>29.6</v>
+      </c>
+      <c r="AB2">
+        <v>0.1713229714353474</v>
+      </c>
+      <c r="AC2">
+        <v>0.1345254587155963</v>
+      </c>
+      <c r="AD2">
+        <v>0.23</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>0.867</v>
+      </c>
+      <c r="AH2">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="AI2">
+        <v>1.476</v>
+      </c>
+      <c r="AJ2">
+        <v>2.08</v>
+      </c>
+      <c r="AK2">
+        <v>2.08</v>
+      </c>
+      <c r="AL2">
+        <v>0.047</v>
+      </c>
+      <c r="AM2">
+        <v>2.08</v>
+      </c>
+      <c r="AN2">
+        <v>0.771</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1813581573436548</v>
+      </c>
+      <c r="C2">
+        <v>32.1354805254252</v>
+      </c>
+      <c r="D2">
+        <v>31.3644805254252</v>
+      </c>
+      <c r="E2">
+        <v>-2.08</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.771</v>
+      </c>
+      <c r="H2">
+        <v>29.6</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.867</v>
+      </c>
+      <c r="K2">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L2">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="O2">
+        <v>0.18653</v>
+      </c>
+      <c r="P2">
+        <v>0.6244700000000001</v>
+      </c>
+      <c r="Q2">
+        <v>0.68047</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1813581573436548</v>
+      </c>
+      <c r="T2">
+        <v>0.8321018258631613</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.23</v>
+      </c>
+      <c r="W2">
+        <v>0.035189</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1809941635817644</v>
+      </c>
+      <c r="C3">
+        <v>31.89896845686075</v>
+      </c>
+      <c r="D3">
+        <v>31.44476845686075</v>
+      </c>
+      <c r="E3">
+        <v>-1.7632</v>
+      </c>
+      <c r="F3">
+        <v>0.3168</v>
+      </c>
+      <c r="G3">
+        <v>0.771</v>
+      </c>
+      <c r="H3">
+        <v>29.6</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0.867</v>
+      </c>
+      <c r="K3">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L3">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M3">
+        <v>0.01447776</v>
+      </c>
+      <c r="N3">
+        <v>0.79652224</v>
+      </c>
+      <c r="O3">
+        <v>0.1832001152</v>
+      </c>
+      <c r="P3">
+        <v>0.6133221248</v>
+      </c>
+      <c r="Q3">
+        <v>0.6693221248</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1824669430118833</v>
+      </c>
+      <c r="T3">
+        <v>0.8385737289532081</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.23</v>
+      </c>
+      <c r="W3">
+        <v>0.035189</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>56.01695289879097</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.180630169819874</v>
+      </c>
+      <c r="C4">
+        <v>31.66286849111243</v>
+      </c>
+      <c r="D4">
+        <v>31.52546849111243</v>
+      </c>
+      <c r="E4">
+        <v>-1.4464</v>
+      </c>
+      <c r="F4">
+        <v>0.6336000000000001</v>
+      </c>
+      <c r="G4">
+        <v>0.771</v>
+      </c>
+      <c r="H4">
+        <v>29.6</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0.867</v>
+      </c>
+      <c r="K4">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L4">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M4">
+        <v>0.02895552000000001</v>
+      </c>
+      <c r="N4">
+        <v>0.78204448</v>
+      </c>
+      <c r="O4">
+        <v>0.1798702304</v>
+      </c>
+      <c r="P4">
+        <v>0.6021742496</v>
+      </c>
+      <c r="Q4">
+        <v>0.6581742495999999</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1835983569590551</v>
+      </c>
+      <c r="T4">
+        <v>0.8451777116981539</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.23</v>
+      </c>
+      <c r="W4">
+        <v>0.035189</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>28.00847644939548</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1802661760579836</v>
+      </c>
+      <c r="C5">
+        <v>31.42718380921317</v>
+      </c>
+      <c r="D5">
+        <v>31.60658380921316</v>
+      </c>
+      <c r="E5">
+        <v>-1.1296</v>
+      </c>
+      <c r="F5">
+        <v>0.9503999999999999</v>
+      </c>
+      <c r="G5">
+        <v>0.771</v>
+      </c>
+      <c r="H5">
+        <v>29.6</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0.867</v>
+      </c>
+      <c r="K5">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L5">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M5">
+        <v>0.04343328</v>
+      </c>
+      <c r="N5">
+        <v>0.76756672</v>
+      </c>
+      <c r="O5">
+        <v>0.1765403456</v>
+      </c>
+      <c r="P5">
+        <v>0.5910263744000001</v>
+      </c>
+      <c r="Q5">
+        <v>0.6470263744</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1847530990288491</v>
+      </c>
+      <c r="T5">
+        <v>0.8519178590357789</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.23</v>
+      </c>
+      <c r="W5">
+        <v>0.035189</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>18.67231763293033</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1799021822960932</v>
+      </c>
+      <c r="C6">
+        <v>31.19191762501963</v>
+      </c>
+      <c r="D6">
+        <v>31.68811762501963</v>
+      </c>
+      <c r="E6">
+        <v>-0.8128</v>
+      </c>
+      <c r="F6">
+        <v>1.2672</v>
+      </c>
+      <c r="G6">
+        <v>0.771</v>
+      </c>
+      <c r="H6">
+        <v>29.6</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0.867</v>
+      </c>
+      <c r="K6">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L6">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M6">
+        <v>0.05791104000000001</v>
+      </c>
+      <c r="N6">
+        <v>0.75308896</v>
+      </c>
+      <c r="O6">
+        <v>0.1732104608</v>
+      </c>
+      <c r="P6">
+        <v>0.5798784992</v>
+      </c>
+      <c r="Q6">
+        <v>0.6358784991999999</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1859318982250971</v>
+      </c>
+      <c r="T6">
+        <v>0.8587984261096043</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.23</v>
+      </c>
+      <c r="W6">
+        <v>0.035189</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>14.00423822469774</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1795997885342028</v>
+      </c>
+      <c r="C7">
+        <v>30.94317375774264</v>
+      </c>
+      <c r="D7">
+        <v>31.75617375774264</v>
+      </c>
+      <c r="E7">
+        <v>-0.496</v>
+      </c>
+      <c r="F7">
+        <v>1.584</v>
+      </c>
+      <c r="G7">
+        <v>0.771</v>
+      </c>
+      <c r="H7">
+        <v>29.6</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0.867</v>
+      </c>
+      <c r="K7">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L7">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M7">
+        <v>0.07492320000000001</v>
+      </c>
+      <c r="N7">
+        <v>0.7360768000000001</v>
+      </c>
+      <c r="O7">
+        <v>0.169297664</v>
+      </c>
+      <c r="P7">
+        <v>0.5667791360000001</v>
+      </c>
+      <c r="Q7">
+        <v>0.622779136</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1871355142465293</v>
+      </c>
+      <c r="T7">
+        <v>0.8658238472270895</v>
+      </c>
+      <c r="U7">
+        <v>0.0473</v>
+      </c>
+      <c r="V7">
+        <v>0.23</v>
+      </c>
+      <c r="W7">
+        <v>0.036421</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>10.82441753689111</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1794236747723124</v>
+      </c>
+      <c r="C8">
+        <v>30.66614443812613</v>
+      </c>
+      <c r="D8">
+        <v>31.79594443812613</v>
+      </c>
+      <c r="E8">
+        <v>-0.1792000000000002</v>
+      </c>
+      <c r="F8">
+        <v>1.9008</v>
+      </c>
+      <c r="G8">
+        <v>0.771</v>
+      </c>
+      <c r="H8">
+        <v>29.6</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0.867</v>
+      </c>
+      <c r="K8">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L8">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M8">
+        <v>0.09713087999999999</v>
+      </c>
+      <c r="N8">
+        <v>0.71386912</v>
+      </c>
+      <c r="O8">
+        <v>0.1641898976</v>
+      </c>
+      <c r="P8">
+        <v>0.5496792224</v>
+      </c>
+      <c r="Q8">
+        <v>0.6056792223999999</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1883647391194813</v>
+      </c>
+      <c r="T8">
+        <v>0.8729987453896272</v>
+      </c>
+      <c r="U8">
+        <v>0.0511</v>
+      </c>
+      <c r="V8">
+        <v>0.23</v>
+      </c>
+      <c r="W8">
+        <v>0.039347</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>8.349558863257496</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1792036710104219</v>
+      </c>
+      <c r="C9">
+        <v>30.39916669233719</v>
+      </c>
+      <c r="D9">
+        <v>31.84576669233719</v>
+      </c>
+      <c r="E9">
+        <v>0.1375999999999999</v>
+      </c>
+      <c r="F9">
+        <v>2.2176</v>
+      </c>
+      <c r="G9">
+        <v>0.771</v>
+      </c>
+      <c r="H9">
+        <v>29.6</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.867</v>
+      </c>
+      <c r="K9">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L9">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M9">
+        <v>0.1175328</v>
+      </c>
+      <c r="N9">
+        <v>0.6934672000000001</v>
+      </c>
+      <c r="O9">
+        <v>0.159497456</v>
+      </c>
+      <c r="P9">
+        <v>0.5339697440000001</v>
+      </c>
+      <c r="Q9">
+        <v>0.589969744</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1896203989359376</v>
+      </c>
+      <c r="T9">
+        <v>0.880327942437381</v>
+      </c>
+      <c r="U9">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V9">
+        <v>0.23</v>
+      </c>
+      <c r="W9">
+        <v>0.04081000000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>6.900201475673174</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1790190872485316</v>
+      </c>
+      <c r="C10">
+        <v>30.12428831322133</v>
+      </c>
+      <c r="D10">
+        <v>31.88768831322134</v>
+      </c>
+      <c r="E10">
+        <v>0.4544000000000001</v>
+      </c>
+      <c r="F10">
+        <v>2.5344</v>
+      </c>
+      <c r="G10">
+        <v>0.771</v>
+      </c>
+      <c r="H10">
+        <v>29.6</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0.867</v>
+      </c>
+      <c r="K10">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L10">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M10">
+        <v>0.139392</v>
+      </c>
+      <c r="N10">
+        <v>0.671608</v>
+      </c>
+      <c r="O10">
+        <v>0.15446984</v>
+      </c>
+      <c r="P10">
+        <v>0.51713816</v>
+      </c>
+      <c r="Q10">
+        <v>0.57313816</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1909033557049256</v>
+      </c>
+      <c r="T10">
+        <v>0.8878164698557381</v>
+      </c>
+      <c r="U10">
+        <v>0.055</v>
+      </c>
+      <c r="V10">
+        <v>0.23</v>
+      </c>
+      <c r="W10">
+        <v>0.04235</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>5.818124426078971</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1787267034866412</v>
+      </c>
+      <c r="C11">
+        <v>29.87411921379064</v>
+      </c>
+      <c r="D11">
+        <v>31.95431921379064</v>
+      </c>
+      <c r="E11">
+        <v>0.7711999999999999</v>
+      </c>
+      <c r="F11">
+        <v>2.8512</v>
+      </c>
+      <c r="G11">
+        <v>0.771</v>
+      </c>
+      <c r="H11">
+        <v>29.6</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0.867</v>
+      </c>
+      <c r="K11">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L11">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M11">
+        <v>0.156816</v>
+      </c>
+      <c r="N11">
+        <v>0.6541840000000001</v>
+      </c>
+      <c r="O11">
+        <v>0.15046232</v>
+      </c>
+      <c r="P11">
+        <v>0.5037216800000001</v>
+      </c>
+      <c r="Q11">
+        <v>0.55972168</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1922145093259793</v>
+      </c>
+      <c r="T11">
+        <v>0.895469580294279</v>
+      </c>
+      <c r="U11">
+        <v>0.055</v>
+      </c>
+      <c r="V11">
+        <v>0.23</v>
+      </c>
+      <c r="W11">
+        <v>0.04235</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>5.171666156514641</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1784343197247508</v>
+      </c>
+      <c r="C12">
+        <v>29.62422915454727</v>
+      </c>
+      <c r="D12">
+        <v>32.02122915454727</v>
+      </c>
+      <c r="E12">
+        <v>1.088</v>
+      </c>
+      <c r="F12">
+        <v>3.168</v>
+      </c>
+      <c r="G12">
+        <v>0.771</v>
+      </c>
+      <c r="H12">
+        <v>29.6</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0.867</v>
+      </c>
+      <c r="K12">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L12">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M12">
+        <v>0.17424</v>
+      </c>
+      <c r="N12">
+        <v>0.63676</v>
+      </c>
+      <c r="O12">
+        <v>0.1464548</v>
+      </c>
+      <c r="P12">
+        <v>0.4903052</v>
+      </c>
+      <c r="Q12">
+        <v>0.5463051999999999</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1935547996941675</v>
+      </c>
+      <c r="T12">
+        <v>0.9032927598536762</v>
+      </c>
+      <c r="U12">
+        <v>0.055</v>
+      </c>
+      <c r="V12">
+        <v>0.23</v>
+      </c>
+      <c r="W12">
+        <v>0.04235</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>4.654499540863177</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1788195359628604</v>
+      </c>
+      <c r="C13">
+        <v>29.21933360880976</v>
+      </c>
+      <c r="D13">
+        <v>31.93313360880976</v>
+      </c>
+      <c r="E13">
+        <v>1.4048</v>
+      </c>
+      <c r="F13">
+        <v>3.4848</v>
+      </c>
+      <c r="G13">
+        <v>0.771</v>
+      </c>
+      <c r="H13">
+        <v>29.6</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0.867</v>
+      </c>
+      <c r="K13">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L13">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M13">
+        <v>0.2195424</v>
+      </c>
+      <c r="N13">
+        <v>0.5914576</v>
+      </c>
+      <c r="O13">
+        <v>0.136035248</v>
+      </c>
+      <c r="P13">
+        <v>0.455422352</v>
+      </c>
+      <c r="Q13">
+        <v>0.511422352</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1949252089470341</v>
+      </c>
+      <c r="T13">
+        <v>0.9112917412009252</v>
+      </c>
+      <c r="U13">
+        <v>0.063</v>
+      </c>
+      <c r="V13">
+        <v>0.23</v>
+      </c>
+      <c r="W13">
+        <v>0.04851</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>3.694047254653315</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.17924479220097</v>
+      </c>
+      <c r="C14">
+        <v>28.80584248871396</v>
+      </c>
+      <c r="D14">
+        <v>31.83644248871397</v>
+      </c>
+      <c r="E14">
+        <v>1.7216</v>
+      </c>
+      <c r="F14">
+        <v>3.8016</v>
+      </c>
+      <c r="G14">
+        <v>0.771</v>
+      </c>
+      <c r="H14">
+        <v>29.6</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0.867</v>
+      </c>
+      <c r="K14">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L14">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M14">
+        <v>0.26649216</v>
+      </c>
+      <c r="N14">
+        <v>0.5445078400000001</v>
+      </c>
+      <c r="O14">
+        <v>0.1252368032</v>
+      </c>
+      <c r="P14">
+        <v>0.4192710368000001</v>
+      </c>
+      <c r="Q14">
+        <v>0.4752710368</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1963267638647386</v>
+      </c>
+      <c r="T14">
+        <v>0.9194725175787932</v>
+      </c>
+      <c r="U14">
+        <v>0.0701</v>
+      </c>
+      <c r="V14">
+        <v>0.23</v>
+      </c>
+      <c r="W14">
+        <v>0.053977</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>3.043241497235792</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1812008084390795</v>
+      </c>
+      <c r="C15">
+        <v>28.05173739786395</v>
+      </c>
+      <c r="D15">
+        <v>31.39913739786396</v>
+      </c>
+      <c r="E15">
+        <v>2.0384</v>
+      </c>
+      <c r="F15">
+        <v>4.1184</v>
+      </c>
+      <c r="G15">
+        <v>0.771</v>
+      </c>
+      <c r="H15">
+        <v>29.6</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0.867</v>
+      </c>
+      <c r="K15">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L15">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M15">
+        <v>0.37642176</v>
+      </c>
+      <c r="N15">
+        <v>0.43457824</v>
+      </c>
+      <c r="O15">
+        <v>0.09995299519999999</v>
+      </c>
+      <c r="P15">
+        <v>0.3346252448</v>
+      </c>
+      <c r="Q15">
+        <v>0.3906252447999999</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1977605384357236</v>
+      </c>
+      <c r="T15">
+        <v>0.9278413577814398</v>
+      </c>
+      <c r="U15">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V15">
+        <v>0.23</v>
+      </c>
+      <c r="W15">
+        <v>0.07037800000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>2.154498188415038</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1811887046771891</v>
+      </c>
+      <c r="C16">
+        <v>27.7376064837545</v>
+      </c>
+      <c r="D16">
+        <v>31.40180648375451</v>
+      </c>
+      <c r="E16">
+        <v>2.3552</v>
+      </c>
+      <c r="F16">
+        <v>4.4352</v>
+      </c>
+      <c r="G16">
+        <v>0.771</v>
+      </c>
+      <c r="H16">
+        <v>29.6</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0.867</v>
+      </c>
+      <c r="K16">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L16">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M16">
+        <v>0.4053772800000001</v>
+      </c>
+      <c r="N16">
+        <v>0.40562272</v>
+      </c>
+      <c r="O16">
+        <v>0.09329322559999999</v>
+      </c>
+      <c r="P16">
+        <v>0.3123294944</v>
+      </c>
+      <c r="Q16">
+        <v>0.3683294944</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1992276566013827</v>
+      </c>
+      <c r="T16">
+        <v>0.9364048221748459</v>
+      </c>
+      <c r="U16">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V16">
+        <v>0.23</v>
+      </c>
+      <c r="W16">
+        <v>0.07037800000000001</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>2.000605460671106</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1836136509152987</v>
+      </c>
+      <c r="C17">
+        <v>26.89497420191276</v>
+      </c>
+      <c r="D17">
+        <v>30.87597420191276</v>
+      </c>
+      <c r="E17">
+        <v>2.672</v>
+      </c>
+      <c r="F17">
+        <v>4.752</v>
+      </c>
+      <c r="G17">
+        <v>0.771</v>
+      </c>
+      <c r="H17">
+        <v>29.6</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0.867</v>
+      </c>
+      <c r="K17">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L17">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M17">
+        <v>0.5346</v>
+      </c>
+      <c r="N17">
+        <v>0.2764000000000001</v>
+      </c>
+      <c r="O17">
+        <v>0.06357200000000002</v>
+      </c>
+      <c r="P17">
+        <v>0.2128280000000001</v>
+      </c>
+      <c r="Q17">
+        <v>0.268828</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.2007292951944691</v>
+      </c>
+      <c r="T17">
+        <v>0.9451697798480968</v>
+      </c>
+      <c r="U17">
+        <v>0.1125</v>
+      </c>
+      <c r="V17">
+        <v>0.23</v>
+      </c>
+      <c r="W17">
+        <v>0.08662500000000001</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>1.517022072577628</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1964487639974717</v>
+      </c>
+      <c r="C18">
+        <v>24.06437954628094</v>
+      </c>
+      <c r="D18">
+        <v>28.36217954628094</v>
+      </c>
+      <c r="E18">
+        <v>2.9888</v>
+      </c>
+      <c r="F18">
+        <v>5.0688</v>
+      </c>
+      <c r="G18">
+        <v>0.771</v>
+      </c>
+      <c r="H18">
+        <v>29.6</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0.867</v>
+      </c>
+      <c r="K18">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L18">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M18">
+        <v>0.9965260800000001</v>
+      </c>
+      <c r="N18">
+        <v>-0.18552608</v>
+      </c>
+      <c r="O18">
+        <v>-0.04267099840000001</v>
+      </c>
+      <c r="P18">
+        <v>-0.1428550816</v>
+      </c>
+      <c r="Q18">
+        <v>-0.08685508160000011</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.203429411805552</v>
+      </c>
+      <c r="T18">
+        <v>0.9609301684781868</v>
+      </c>
+      <c r="U18">
+        <v>0.1966</v>
+      </c>
+      <c r="V18">
+        <v>0.1871802492113402</v>
+      </c>
+      <c r="W18">
+        <v>0.1598003630050505</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.813827170484088</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.2012942371712054</v>
+      </c>
+      <c r="C19">
+        <v>22.90183767547647</v>
+      </c>
+      <c r="D19">
+        <v>27.51643767547647</v>
+      </c>
+      <c r="E19">
+        <v>3.3056</v>
+      </c>
+      <c r="F19">
+        <v>5.3856</v>
+      </c>
+      <c r="G19">
+        <v>0.771</v>
+      </c>
+      <c r="H19">
+        <v>29.6</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0.867</v>
+      </c>
+      <c r="K19">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L19">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M19">
+        <v>1.15144128</v>
+      </c>
+      <c r="N19">
+        <v>-0.34044128</v>
+      </c>
+      <c r="O19">
+        <v>-0.07830149439999999</v>
+      </c>
+      <c r="P19">
+        <v>-0.2621397856</v>
+      </c>
+      <c r="Q19">
+        <v>-0.2061397856</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.2058267217956594</v>
+      </c>
+      <c r="T19">
+        <v>0.974923096396858</v>
+      </c>
+      <c r="U19">
+        <v>0.2138</v>
+      </c>
+      <c r="V19">
+        <v>0.1619969713088626</v>
+      </c>
+      <c r="W19">
+        <v>0.1791650475341652</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.7043346578646199</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.2030442371712054</v>
+      </c>
+      <c r="C20">
+        <v>22.29185377592881</v>
+      </c>
+      <c r="D20">
+        <v>27.22325377592881</v>
+      </c>
+      <c r="E20">
+        <v>3.6224</v>
+      </c>
+      <c r="F20">
+        <v>5.7024</v>
+      </c>
+      <c r="G20">
+        <v>0.771</v>
+      </c>
+      <c r="H20">
+        <v>29.6</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0.867</v>
+      </c>
+      <c r="K20">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L20">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M20">
+        <v>1.21917312</v>
+      </c>
+      <c r="N20">
+        <v>-0.4081731199999999</v>
+      </c>
+      <c r="O20">
+        <v>-0.09387981759999998</v>
+      </c>
+      <c r="P20">
+        <v>-0.3142933024</v>
+      </c>
+      <c r="Q20">
+        <v>-0.2582933024</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.2078636330370699</v>
+      </c>
+      <c r="T20">
+        <v>0.9868124024504782</v>
+      </c>
+      <c r="U20">
+        <v>0.2138</v>
+      </c>
+      <c r="V20">
+        <v>0.1529971395694813</v>
+      </c>
+      <c r="W20">
+        <v>0.1810892115600449</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.6652049546499188</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.2047942371712054</v>
+      </c>
+      <c r="C21">
+        <v>21.68805167923109</v>
+      </c>
+      <c r="D21">
+        <v>26.93625167923108</v>
+      </c>
+      <c r="E21">
+        <v>3.9392</v>
+      </c>
+      <c r="F21">
+        <v>6.0192</v>
+      </c>
+      <c r="G21">
+        <v>0.771</v>
+      </c>
+      <c r="H21">
+        <v>29.6</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0.867</v>
+      </c>
+      <c r="K21">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L21">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M21">
+        <v>1.28690496</v>
+      </c>
+      <c r="N21">
+        <v>-0.4759049599999997</v>
+      </c>
+      <c r="O21">
+        <v>-0.1094581407999999</v>
+      </c>
+      <c r="P21">
+        <v>-0.3664468191999998</v>
+      </c>
+      <c r="Q21">
+        <v>-0.3104468191999998</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.2099508383832066</v>
+      </c>
+      <c r="T21">
+        <v>0.9989952716165336</v>
+      </c>
+      <c r="U21">
+        <v>0.2138</v>
+      </c>
+      <c r="V21">
+        <v>0.1449446585395086</v>
+      </c>
+      <c r="W21">
+        <v>0.182810832004253</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.6301941675630811</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.2065442371712054</v>
+      </c>
+      <c r="C22">
+        <v>21.09023790949696</v>
+      </c>
+      <c r="D22">
+        <v>26.65523790949696</v>
+      </c>
+      <c r="E22">
+        <v>4.256</v>
+      </c>
+      <c r="F22">
+        <v>6.336</v>
+      </c>
+      <c r="G22">
+        <v>0.771</v>
+      </c>
+      <c r="H22">
+        <v>29.6</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0.867</v>
+      </c>
+      <c r="K22">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L22">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M22">
+        <v>1.3546368</v>
+      </c>
+      <c r="N22">
+        <v>-0.5436367999999999</v>
+      </c>
+      <c r="O22">
+        <v>-0.125036464</v>
+      </c>
+      <c r="P22">
+        <v>-0.418600336</v>
+      </c>
+      <c r="Q22">
+        <v>-0.362600336</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.2120902238629966</v>
+      </c>
+      <c r="T22">
+        <v>1.01148271251174</v>
+      </c>
+      <c r="U22">
+        <v>0.2138</v>
+      </c>
+      <c r="V22">
+        <v>0.1376974256125332</v>
+      </c>
+      <c r="W22">
+        <v>0.1843602904040404</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.598684459184927</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.2082942371712054</v>
+      </c>
+      <c r="C23">
+        <v>20.4982269812664</v>
+      </c>
+      <c r="D23">
+        <v>26.3800269812664</v>
+      </c>
+      <c r="E23">
+        <v>4.5728</v>
+      </c>
+      <c r="F23">
+        <v>6.6528</v>
+      </c>
+      <c r="G23">
+        <v>0.771</v>
+      </c>
+      <c r="H23">
+        <v>29.6</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0.867</v>
+      </c>
+      <c r="K23">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L23">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M23">
+        <v>1.42236864</v>
+      </c>
+      <c r="N23">
+        <v>-0.6113686399999999</v>
+      </c>
+      <c r="O23">
+        <v>-0.1406147872</v>
+      </c>
+      <c r="P23">
+        <v>-0.4707538527999999</v>
+      </c>
+      <c r="Q23">
+        <v>-0.4147538528</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.2142837710005029</v>
+      </c>
+      <c r="T23">
+        <v>1.024286291151129</v>
+      </c>
+      <c r="U23">
+        <v>0.2138</v>
+      </c>
+      <c r="V23">
+        <v>0.1311404053452697</v>
+      </c>
+      <c r="W23">
+        <v>0.1857621813371813</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.5701756754142162</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.2100442371712054</v>
+      </c>
+      <c r="C24">
+        <v>19.91184099122188</v>
+      </c>
+      <c r="D24">
+        <v>26.11044099122188</v>
+      </c>
+      <c r="E24">
+        <v>4.8896</v>
+      </c>
+      <c r="F24">
+        <v>6.9696</v>
+      </c>
+      <c r="G24">
+        <v>0.771</v>
+      </c>
+      <c r="H24">
+        <v>29.6</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0.867</v>
+      </c>
+      <c r="K24">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L24">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M24">
+        <v>1.49010048</v>
+      </c>
+      <c r="N24">
+        <v>-0.6791004799999999</v>
+      </c>
+      <c r="O24">
+        <v>-0.1561931104</v>
+      </c>
+      <c r="P24">
+        <v>-0.5229073695999999</v>
+      </c>
+      <c r="Q24">
+        <v>-0.4669073696</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.2165335629364068</v>
+      </c>
+      <c r="T24">
+        <v>1.037418166678708</v>
+      </c>
+      <c r="U24">
+        <v>0.2138</v>
+      </c>
+      <c r="V24">
+        <v>0.1251794778295756</v>
+      </c>
+      <c r="W24">
+        <v>0.1870366276400367</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.5442585992590245</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.2117942371712054</v>
+      </c>
+      <c r="C25">
+        <v>19.33090923468588</v>
+      </c>
+      <c r="D25">
+        <v>25.84630923468588</v>
+      </c>
+      <c r="E25">
+        <v>5.2064</v>
+      </c>
+      <c r="F25">
+        <v>7.2864</v>
+      </c>
+      <c r="G25">
+        <v>0.771</v>
+      </c>
+      <c r="H25">
+        <v>29.6</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0.867</v>
+      </c>
+      <c r="K25">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L25">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M25">
+        <v>1.55783232</v>
+      </c>
+      <c r="N25">
+        <v>-0.7468323199999999</v>
+      </c>
+      <c r="O25">
+        <v>-0.1717714336</v>
+      </c>
+      <c r="P25">
+        <v>-0.5750608864</v>
+      </c>
+      <c r="Q25">
+        <v>-0.5190608864</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.21884179102649</v>
+      </c>
+      <c r="T25">
+        <v>1.050891129882328</v>
+      </c>
+      <c r="U25">
+        <v>0.2138</v>
+      </c>
+      <c r="V25">
+        <v>0.1197368918369854</v>
+      </c>
+      <c r="W25">
+        <v>0.1882002525252525</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.5205951818999365</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.2199552482948713</v>
+      </c>
+      <c r="C26">
+        <v>17.84973768511508</v>
+      </c>
+      <c r="D26">
+        <v>24.68193768511508</v>
+      </c>
+      <c r="E26">
+        <v>5.523199999999999</v>
+      </c>
+      <c r="F26">
+        <v>7.603199999999999</v>
+      </c>
+      <c r="G26">
+        <v>0.771</v>
+      </c>
+      <c r="H26">
+        <v>29.6</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0.867</v>
+      </c>
+      <c r="K26">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L26">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M26">
+        <v>1.81564416</v>
+      </c>
+      <c r="N26">
+        <v>-1.00464416</v>
+      </c>
+      <c r="O26">
+        <v>-0.2310681567999999</v>
+      </c>
+      <c r="P26">
+        <v>-0.7735760031999999</v>
+      </c>
+      <c r="Q26">
+        <v>-0.7175760031999999</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.2217515660711359</v>
+      </c>
+      <c r="T26">
+        <v>1.067875279878488</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.1027348883164419</v>
+      </c>
+      <c r="W26">
+        <v>0.2142669086700337</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.446673427462791</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.2219552482948713</v>
+      </c>
+      <c r="C27">
+        <v>17.26341837933599</v>
+      </c>
+      <c r="D27">
+        <v>24.41241837933599</v>
+      </c>
+      <c r="E27">
+        <v>5.84</v>
+      </c>
+      <c r="F27">
+        <v>7.92</v>
+      </c>
+      <c r="G27">
+        <v>0.771</v>
+      </c>
+      <c r="H27">
+        <v>29.6</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0.867</v>
+      </c>
+      <c r="K27">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L27">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M27">
+        <v>1.891296</v>
+      </c>
+      <c r="N27">
+        <v>-1.080296</v>
+      </c>
+      <c r="O27">
+        <v>-0.24846808</v>
+      </c>
+      <c r="P27">
+        <v>-0.8318279200000002</v>
+      </c>
+      <c r="Q27">
+        <v>-0.7758279200000002</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.2241909202854177</v>
+      </c>
+      <c r="T27">
+        <v>1.082113616943535</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.09862549278378424</v>
+      </c>
+      <c r="W27">
+        <v>0.2152482323232323</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.4288064903642793</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.2239552482948713</v>
+      </c>
+      <c r="C28">
+        <v>16.68292163183189</v>
+      </c>
+      <c r="D28">
+        <v>24.14872163183189</v>
+      </c>
+      <c r="E28">
+        <v>6.1568</v>
+      </c>
+      <c r="F28">
+        <v>8.236800000000001</v>
+      </c>
+      <c r="G28">
+        <v>0.771</v>
+      </c>
+      <c r="H28">
+        <v>29.6</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0.867</v>
+      </c>
+      <c r="K28">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L28">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M28">
+        <v>1.96694784</v>
+      </c>
+      <c r="N28">
+        <v>-1.15594784</v>
+      </c>
+      <c r="O28">
+        <v>-0.2658680032</v>
+      </c>
+      <c r="P28">
+        <v>-0.8900798368</v>
+      </c>
+      <c r="Q28">
+        <v>-0.8340798368000001</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.2266962029919774</v>
+      </c>
+      <c r="T28">
+        <v>1.096736773929258</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.09483220459979252</v>
+      </c>
+      <c r="W28">
+        <v>0.2161540695415696</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.4123139330425762</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.2259552482948713</v>
+      </c>
+      <c r="C29">
+        <v>16.10806077752142</v>
+      </c>
+      <c r="D29">
+        <v>23.89066077752141</v>
+      </c>
+      <c r="E29">
+        <v>6.473600000000001</v>
+      </c>
+      <c r="F29">
+        <v>8.553600000000001</v>
+      </c>
+      <c r="G29">
+        <v>0.771</v>
+      </c>
+      <c r="H29">
+        <v>29.6</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0.867</v>
+      </c>
+      <c r="K29">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L29">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M29">
+        <v>2.04259968</v>
+      </c>
+      <c r="N29">
+        <v>-1.23159968</v>
+      </c>
+      <c r="O29">
+        <v>-0.2832679264000001</v>
+      </c>
+      <c r="P29">
+        <v>-0.9483317536000003</v>
+      </c>
+      <c r="Q29">
+        <v>-0.8923317536000004</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.2292701235809086</v>
+      </c>
+      <c r="T29">
+        <v>1.111760565352947</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.09131990072572613</v>
+      </c>
+      <c r="W29">
+        <v>0.2169928077066966</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.3970430466335918</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.2279552482948714</v>
+      </c>
+      <c r="C30">
+        <v>15.53865704600581</v>
+      </c>
+      <c r="D30">
+        <v>23.63805704600581</v>
+      </c>
+      <c r="E30">
+        <v>6.7904</v>
+      </c>
+      <c r="F30">
+        <v>8.8704</v>
+      </c>
+      <c r="G30">
+        <v>0.771</v>
+      </c>
+      <c r="H30">
+        <v>29.6</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0.867</v>
+      </c>
+      <c r="K30">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L30">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M30">
+        <v>2.11825152</v>
+      </c>
+      <c r="N30">
+        <v>-1.30725152</v>
+      </c>
+      <c r="O30">
+        <v>-0.3006678496</v>
+      </c>
+      <c r="P30">
+        <v>-1.0065836704</v>
+      </c>
+      <c r="Q30">
+        <v>-0.9505836704000005</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.2319155419639768</v>
+      </c>
+      <c r="T30">
+        <v>1.127201684316182</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.08805847569980735</v>
+      </c>
+      <c r="W30">
+        <v>0.217771636002886</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.3828629378252493</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.2299552482948714</v>
+      </c>
+      <c r="C31">
+        <v>14.97453914857051</v>
+      </c>
+      <c r="D31">
+        <v>23.39073914857051</v>
+      </c>
+      <c r="E31">
+        <v>7.107199999999999</v>
+      </c>
+      <c r="F31">
+        <v>9.187199999999999</v>
+      </c>
+      <c r="G31">
+        <v>0.771</v>
+      </c>
+      <c r="H31">
+        <v>29.6</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0.867</v>
+      </c>
+      <c r="K31">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L31">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M31">
+        <v>2.19390336</v>
+      </c>
+      <c r="N31">
+        <v>-1.38290336</v>
+      </c>
+      <c r="O31">
+        <v>-0.3180677727999999</v>
+      </c>
+      <c r="P31">
+        <v>-1.0648355872</v>
+      </c>
+      <c r="Q31">
+        <v>-1.0088355872</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.234635479174737</v>
+      </c>
+      <c r="T31">
+        <v>1.143077764376973</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.08502197653774504</v>
+      </c>
+      <c r="W31">
+        <v>0.2184967520027865</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.3696607675554132</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.2319552482948714</v>
+      </c>
+      <c r="C32">
+        <v>14.41554289084458</v>
+      </c>
+      <c r="D32">
+        <v>23.14854289084458</v>
+      </c>
+      <c r="E32">
+        <v>7.423999999999999</v>
+      </c>
+      <c r="F32">
+        <v>9.504</v>
+      </c>
+      <c r="G32">
+        <v>0.771</v>
+      </c>
+      <c r="H32">
+        <v>29.6</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0.867</v>
+      </c>
+      <c r="K32">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L32">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M32">
+        <v>2.2695552</v>
+      </c>
+      <c r="N32">
+        <v>-1.4585552</v>
+      </c>
+      <c r="O32">
+        <v>-0.335467696</v>
+      </c>
+      <c r="P32">
+        <v>-1.123087504</v>
+      </c>
+      <c r="Q32">
+        <v>-1.067087504</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.2374331288772333</v>
+      </c>
+      <c r="T32">
+        <v>1.159407446725216</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.08218791065315352</v>
+      </c>
+      <c r="W32">
+        <v>0.2191735269360269</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.3573387419702327</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.2339552482948714</v>
+      </c>
+      <c r="C33">
+        <v>13.86151080927772</v>
+      </c>
+      <c r="D33">
+        <v>22.91131080927772</v>
+      </c>
+      <c r="E33">
+        <v>7.7408</v>
+      </c>
+      <c r="F33">
+        <v>9.8208</v>
+      </c>
+      <c r="G33">
+        <v>0.771</v>
+      </c>
+      <c r="H33">
+        <v>29.6</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0.867</v>
+      </c>
+      <c r="K33">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L33">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M33">
+        <v>2.34520704</v>
+      </c>
+      <c r="N33">
+        <v>-1.53420704</v>
+      </c>
+      <c r="O33">
+        <v>-0.3528676192</v>
+      </c>
+      <c r="P33">
+        <v>-1.1813394208</v>
+      </c>
+      <c r="Q33">
+        <v>-1.1253394208</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.2403118698754541</v>
+      </c>
+      <c r="T33">
+        <v>1.176210453199494</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.07953668772885826</v>
+      </c>
+      <c r="W33">
+        <v>0.2198066389703487</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.3458116857776445</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.2359552482948714</v>
+      </c>
+      <c r="C34">
+        <v>13.31229182974327</v>
+      </c>
+      <c r="D34">
+        <v>22.67889182974327</v>
+      </c>
+      <c r="E34">
+        <v>8.057600000000001</v>
+      </c>
+      <c r="F34">
+        <v>10.1376</v>
+      </c>
+      <c r="G34">
+        <v>0.771</v>
+      </c>
+      <c r="H34">
+        <v>29.6</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0.867</v>
+      </c>
+      <c r="K34">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L34">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M34">
+        <v>2.42085888</v>
+      </c>
+      <c r="N34">
+        <v>-1.60985888</v>
+      </c>
+      <c r="O34">
+        <v>-0.3702675424000001</v>
+      </c>
+      <c r="P34">
+        <v>-1.2395913376</v>
+      </c>
+      <c r="Q34">
+        <v>-1.1835913376</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.2432752797265637</v>
+      </c>
+      <c r="T34">
+        <v>1.193507665746546</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.07705116623733142</v>
+      </c>
+      <c r="W34">
+        <v>0.2204001815025253</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.3350050705970932</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.2379552482948714</v>
+      </c>
+      <c r="C35">
+        <v>12.76774094671191</v>
+      </c>
+      <c r="D35">
+        <v>22.45114094671191</v>
+      </c>
+      <c r="E35">
+        <v>8.3744</v>
+      </c>
+      <c r="F35">
+        <v>10.4544</v>
+      </c>
+      <c r="G35">
+        <v>0.771</v>
+      </c>
+      <c r="H35">
+        <v>29.6</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0.867</v>
+      </c>
+      <c r="K35">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L35">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M35">
+        <v>2.49651072</v>
+      </c>
+      <c r="N35">
+        <v>-1.68551072</v>
+      </c>
+      <c r="O35">
+        <v>-0.3876674655999999</v>
+      </c>
+      <c r="P35">
+        <v>-1.2978432544</v>
+      </c>
+      <c r="Q35">
+        <v>-1.2418432544</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.2463271495732288</v>
+      </c>
+      <c r="T35">
+        <v>1.211321212996494</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.07471628241195775</v>
+      </c>
+      <c r="W35">
+        <v>0.2209577517600245</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.3248534017911207</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.2399552482948714</v>
+      </c>
+      <c r="C36">
+        <v>12.22771892156444</v>
+      </c>
+      <c r="D36">
+        <v>22.22791892156444</v>
+      </c>
+      <c r="E36">
+        <v>8.6912</v>
+      </c>
+      <c r="F36">
+        <v>10.7712</v>
+      </c>
+      <c r="G36">
+        <v>0.771</v>
+      </c>
+      <c r="H36">
+        <v>29.6</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0.867</v>
+      </c>
+      <c r="K36">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L36">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M36">
+        <v>2.57216256</v>
+      </c>
+      <c r="N36">
+        <v>-1.76116256</v>
+      </c>
+      <c r="O36">
+        <v>-0.4050673888</v>
+      </c>
+      <c r="P36">
+        <v>-1.3560951712</v>
+      </c>
+      <c r="Q36">
+        <v>-1.3000951712</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.2494715003243383</v>
+      </c>
+      <c r="T36">
+        <v>1.229674564708562</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.072518744693959</v>
+      </c>
+      <c r="W36">
+        <v>0.2214825237670826</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.3152988899737348</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.2419552482948714</v>
+      </c>
+      <c r="C37">
+        <v>11.69209199872461</v>
+      </c>
+      <c r="D37">
+        <v>22.00909199872461</v>
+      </c>
+      <c r="E37">
+        <v>9.008000000000001</v>
+      </c>
+      <c r="F37">
+        <v>11.088</v>
+      </c>
+      <c r="G37">
+        <v>0.771</v>
+      </c>
+      <c r="H37">
+        <v>29.6</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0.867</v>
+      </c>
+      <c r="K37">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L37">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M37">
+        <v>2.647814400000001</v>
+      </c>
+      <c r="N37">
+        <v>-1.836814400000001</v>
+      </c>
+      <c r="O37">
+        <v>-0.4224673120000001</v>
+      </c>
+      <c r="P37">
+        <v>-1.414347088</v>
+      </c>
+      <c r="Q37">
+        <v>-1.358347088</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.2527126003293282</v>
+      </c>
+      <c r="T37">
+        <v>1.248592634934848</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.07044678055984586</v>
+      </c>
+      <c r="W37">
+        <v>0.2219773088023088</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.3062903502601995</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.2439552482948714</v>
+      </c>
+      <c r="C38">
+        <v>11.16073163839602</v>
+      </c>
+      <c r="D38">
+        <v>21.79453163839602</v>
+      </c>
+      <c r="E38">
+        <v>9.3248</v>
+      </c>
+      <c r="F38">
+        <v>11.4048</v>
+      </c>
+      <c r="G38">
+        <v>0.771</v>
+      </c>
+      <c r="H38">
+        <v>29.6</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0.867</v>
+      </c>
+      <c r="K38">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L38">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M38">
+        <v>2.72346624</v>
+      </c>
+      <c r="N38">
+        <v>-1.91246624</v>
+      </c>
+      <c r="O38">
+        <v>-0.4398672352</v>
+      </c>
+      <c r="P38">
+        <v>-1.4725990048</v>
+      </c>
+      <c r="Q38">
+        <v>-1.4165990048</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.2560549847094739</v>
+      </c>
+      <c r="T38">
+        <v>1.268101894855705</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.06848992554429462</v>
+      </c>
+      <c r="W38">
+        <v>0.2224446057800225</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.297782284975194</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2459552482948714</v>
+      </c>
+      <c r="C39">
+        <v>10.63351426478091</v>
+      </c>
+      <c r="D39">
+        <v>21.58411426478091</v>
+      </c>
+      <c r="E39">
+        <v>9.6416</v>
+      </c>
+      <c r="F39">
+        <v>11.7216</v>
+      </c>
+      <c r="G39">
+        <v>0.771</v>
+      </c>
+      <c r="H39">
+        <v>29.6</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0.867</v>
+      </c>
+      <c r="K39">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L39">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M39">
+        <v>2.79911808</v>
+      </c>
+      <c r="N39">
+        <v>-1.98811808</v>
+      </c>
+      <c r="O39">
+        <v>-0.4572671584000001</v>
+      </c>
+      <c r="P39">
+        <v>-1.5308509216</v>
+      </c>
+      <c r="Q39">
+        <v>-1.4748509216</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.2595034765302592</v>
+      </c>
+      <c r="T39">
+        <v>1.288230496361351</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.06663884647552988</v>
+      </c>
+      <c r="W39">
+        <v>0.2228866434616435</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.2897341151109994</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2479552482948714</v>
+      </c>
+      <c r="C40">
+        <v>10.11032102874457</v>
+      </c>
+      <c r="D40">
+        <v>21.37772102874457</v>
+      </c>
+      <c r="E40">
+        <v>9.958399999999999</v>
+      </c>
+      <c r="F40">
+        <v>12.0384</v>
+      </c>
+      <c r="G40">
+        <v>0.771</v>
+      </c>
+      <c r="H40">
+        <v>29.6</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0.867</v>
+      </c>
+      <c r="K40">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L40">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M40">
+        <v>2.87476992</v>
+      </c>
+      <c r="N40">
+        <v>-2.06376992</v>
+      </c>
+      <c r="O40">
+        <v>-0.4746670815999999</v>
+      </c>
+      <c r="P40">
+        <v>-1.5891028384</v>
+      </c>
+      <c r="Q40">
+        <v>-1.5331028384</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.2630632100226827</v>
+      </c>
+      <c r="T40">
+        <v>1.309008407592986</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.06488519262091068</v>
+      </c>
+      <c r="W40">
+        <v>0.2233054160021266</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.2821095331343942</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2499552482948714</v>
+      </c>
+      <c r="C41">
+        <v>9.591037583967569</v>
+      </c>
+      <c r="D41">
+        <v>21.17523758396757</v>
+      </c>
+      <c r="E41">
+        <v>10.2752</v>
+      </c>
+      <c r="F41">
+        <v>12.3552</v>
+      </c>
+      <c r="G41">
+        <v>0.771</v>
+      </c>
+      <c r="H41">
+        <v>29.6</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0.867</v>
+      </c>
+      <c r="K41">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L41">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M41">
+        <v>2.95042176</v>
+      </c>
+      <c r="N41">
+        <v>-2.13942176</v>
+      </c>
+      <c r="O41">
+        <v>-0.4920670048</v>
+      </c>
+      <c r="P41">
+        <v>-1.6473547552</v>
+      </c>
+      <c r="Q41">
+        <v>-1.5913547552</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.2667396560886283</v>
+      </c>
+      <c r="T41">
+        <v>1.330467561815821</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.06322146973319502</v>
+      </c>
+      <c r="W41">
+        <v>0.2237027130277131</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.2748759553617175</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2519552482948714</v>
+      </c>
+      <c r="C42">
+        <v>9.075553875699928</v>
+      </c>
+      <c r="D42">
+        <v>20.97655387569993</v>
+      </c>
+      <c r="E42">
+        <v>10.592</v>
+      </c>
+      <c r="F42">
+        <v>12.672</v>
+      </c>
+      <c r="G42">
+        <v>0.771</v>
+      </c>
+      <c r="H42">
+        <v>29.6</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0.867</v>
+      </c>
+      <c r="K42">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L42">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M42">
+        <v>3.0260736</v>
+      </c>
+      <c r="N42">
+        <v>-2.2150736</v>
+      </c>
+      <c r="O42">
+        <v>-0.509466928</v>
+      </c>
+      <c r="P42">
+        <v>-1.705606672</v>
+      </c>
+      <c r="Q42">
+        <v>-1.649606672</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.2705386503567722</v>
+      </c>
+      <c r="T42">
+        <v>1.352642021179419</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.06164093298986514</v>
+      </c>
+      <c r="W42">
+        <v>0.2240801452020202</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.2680040564776746</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2539552482948714</v>
+      </c>
+      <c r="C43">
+        <v>8.563763941297289</v>
+      </c>
+      <c r="D43">
+        <v>20.78156394129729</v>
+      </c>
+      <c r="E43">
+        <v>10.9088</v>
+      </c>
+      <c r="F43">
+        <v>12.9888</v>
+      </c>
+      <c r="G43">
+        <v>0.771</v>
+      </c>
+      <c r="H43">
+        <v>29.6</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0.867</v>
+      </c>
+      <c r="K43">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L43">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M43">
+        <v>3.10172544</v>
+      </c>
+      <c r="N43">
+        <v>-2.290725440000001</v>
+      </c>
+      <c r="O43">
+        <v>-0.5268668512000001</v>
+      </c>
+      <c r="P43">
+        <v>-1.7638585888</v>
+      </c>
+      <c r="Q43">
+        <v>-1.707858588800001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.2744664240916327</v>
+      </c>
+      <c r="T43">
+        <v>1.375568157131612</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.06013749559986843</v>
+      </c>
+      <c r="W43">
+        <v>0.2244391660507514</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.2614673721733409</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2559552482948714</v>
+      </c>
+      <c r="C44">
+        <v>8.055565721779443</v>
+      </c>
+      <c r="D44">
+        <v>20.59016572177944</v>
+      </c>
+      <c r="E44">
+        <v>11.2256</v>
+      </c>
+      <c r="F44">
+        <v>13.3056</v>
+      </c>
+      <c r="G44">
+        <v>0.771</v>
+      </c>
+      <c r="H44">
+        <v>29.6</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0.867</v>
+      </c>
+      <c r="K44">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L44">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M44">
+        <v>3.17737728</v>
+      </c>
+      <c r="N44">
+        <v>-2.36637728</v>
+      </c>
+      <c r="O44">
+        <v>-0.5442667743999999</v>
+      </c>
+      <c r="P44">
+        <v>-1.8221105056</v>
+      </c>
+      <c r="Q44">
+        <v>-1.7661105056</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.2785296383001091</v>
+      </c>
+      <c r="T44">
+        <v>1.39928484949595</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.05870565046653824</v>
+      </c>
+      <c r="W44">
+        <v>0.2247810906685907</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.2552419585501663</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2579552482948714</v>
+      </c>
+      <c r="C45">
+        <v>7.55086088370707</v>
+      </c>
+      <c r="D45">
+        <v>20.40226088370707</v>
+      </c>
+      <c r="E45">
+        <v>11.5424</v>
+      </c>
+      <c r="F45">
+        <v>13.6224</v>
+      </c>
+      <c r="G45">
+        <v>0.771</v>
+      </c>
+      <c r="H45">
+        <v>29.6</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0.867</v>
+      </c>
+      <c r="K45">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L45">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M45">
+        <v>3.25302912</v>
+      </c>
+      <c r="N45">
+        <v>-2.44202912</v>
+      </c>
+      <c r="O45">
+        <v>-0.5616666976</v>
+      </c>
+      <c r="P45">
+        <v>-1.8803624224</v>
+      </c>
+      <c r="Q45">
+        <v>-1.8243624224</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2827354214281811</v>
+      </c>
+      <c r="T45">
+        <v>1.423833706504651</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.05734040278126991</v>
+      </c>
+      <c r="W45">
+        <v>0.2251071118158328</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.2493060990489996</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2599552482948714</v>
+      </c>
+      <c r="C46">
+        <v>7.049554650723582</v>
+      </c>
+      <c r="D46">
+        <v>20.21775465072358</v>
+      </c>
+      <c r="E46">
+        <v>11.8592</v>
+      </c>
+      <c r="F46">
+        <v>13.9392</v>
+      </c>
+      <c r="G46">
+        <v>0.771</v>
+      </c>
+      <c r="H46">
+        <v>29.6</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0.867</v>
+      </c>
+      <c r="K46">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L46">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M46">
+        <v>3.32868096</v>
+      </c>
+      <c r="N46">
+        <v>-2.51768096</v>
+      </c>
+      <c r="O46">
+        <v>-0.5790666208</v>
+      </c>
+      <c r="P46">
+        <v>-1.9386143392</v>
+      </c>
+      <c r="Q46">
+        <v>-1.8826143392</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2870914110965416</v>
+      </c>
+      <c r="T46">
+        <v>1.44925930840652</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.05603721180896831</v>
+      </c>
+      <c r="W46">
+        <v>0.2254183138200184</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.2436400513433404</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2619552482948714</v>
+      </c>
+      <c r="C47">
+        <v>6.551555644155666</v>
+      </c>
+      <c r="D47">
+        <v>20.03655564415567</v>
+      </c>
+      <c r="E47">
+        <v>12.176</v>
+      </c>
+      <c r="F47">
+        <v>14.256</v>
+      </c>
+      <c r="G47">
+        <v>0.771</v>
+      </c>
+      <c r="H47">
+        <v>29.6</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0.867</v>
+      </c>
+      <c r="K47">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L47">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M47">
+        <v>3.4043328</v>
+      </c>
+      <c r="N47">
+        <v>-2.5933328</v>
+      </c>
+      <c r="O47">
+        <v>-0.596466544</v>
+      </c>
+      <c r="P47">
+        <v>-1.996866256</v>
+      </c>
+      <c r="Q47">
+        <v>-1.940866256</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.291605800389206</v>
+      </c>
+      <c r="T47">
+        <v>1.475609477650275</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.05479194043543568</v>
+      </c>
+      <c r="W47">
+        <v>0.225715684624018</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.2382258279801551</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2639552482948714</v>
+      </c>
+      <c r="C48">
+        <v>6.056775732109244</v>
+      </c>
+      <c r="D48">
+        <v>19.85857573210924</v>
+      </c>
+      <c r="E48">
+        <v>12.4928</v>
+      </c>
+      <c r="F48">
+        <v>14.5728</v>
+      </c>
+      <c r="G48">
+        <v>0.771</v>
+      </c>
+      <c r="H48">
+        <v>29.6</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0.867</v>
+      </c>
+      <c r="K48">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L48">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M48">
+        <v>3.479984640000001</v>
+      </c>
+      <c r="N48">
+        <v>-2.668984640000001</v>
+      </c>
+      <c r="O48">
+        <v>-0.6138664672</v>
+      </c>
+      <c r="P48">
+        <v>-2.0551181728</v>
+      </c>
+      <c r="Q48">
+        <v>-1.9991181728</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2962873892853024</v>
+      </c>
+      <c r="T48">
+        <v>1.502935579088243</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.05360081129553491</v>
+      </c>
+      <c r="W48">
+        <v>0.2260001262626263</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.2330470056327605</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2659552482948714</v>
+      </c>
+      <c r="C49">
+        <v>5.565129886537314</v>
+      </c>
+      <c r="D49">
+        <v>19.68372988653731</v>
+      </c>
+      <c r="E49">
+        <v>12.8096</v>
+      </c>
+      <c r="F49">
+        <v>14.8896</v>
+      </c>
+      <c r="G49">
+        <v>0.771</v>
+      </c>
+      <c r="H49">
+        <v>29.6</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0.867</v>
+      </c>
+      <c r="K49">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L49">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M49">
+        <v>3.55563648</v>
+      </c>
+      <c r="N49">
+        <v>-2.74463648</v>
+      </c>
+      <c r="O49">
+        <v>-0.6312663904000001</v>
+      </c>
+      <c r="P49">
+        <v>-2.113370089600001</v>
+      </c>
+      <c r="Q49">
+        <v>-2.0573700896</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.3011456419133269</v>
+      </c>
+      <c r="T49">
+        <v>1.531292854165379</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.05246036850201288</v>
+      </c>
+      <c r="W49">
+        <v>0.2262724640017194</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.2280885587044038</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2679552482948713</v>
+      </c>
+      <c r="C50">
+        <v>5.076536047792604</v>
+      </c>
+      <c r="D50">
+        <v>19.5119360477926</v>
+      </c>
+      <c r="E50">
+        <v>13.1264</v>
+      </c>
+      <c r="F50">
+        <v>15.2064</v>
+      </c>
+      <c r="G50">
+        <v>0.771</v>
+      </c>
+      <c r="H50">
+        <v>29.6</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0.867</v>
+      </c>
+      <c r="K50">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L50">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M50">
+        <v>3.63128832</v>
+      </c>
+      <c r="N50">
+        <v>-2.82028832</v>
+      </c>
+      <c r="O50">
+        <v>-0.6486663135999999</v>
+      </c>
+      <c r="P50">
+        <v>-2.1716220064</v>
+      </c>
+      <c r="Q50">
+        <v>-2.1156220064</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.3061907504116601</v>
+      </c>
+      <c r="T50">
+        <v>1.56074079366856</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.05136744415822096</v>
+      </c>
+      <c r="W50">
+        <v>0.2265334543350168</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.2233367137313954</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2699552482948714</v>
+      </c>
+      <c r="C51">
+        <v>4.590914996211694</v>
+      </c>
+      <c r="D51">
+        <v>19.34311499621169</v>
+      </c>
+      <c r="E51">
+        <v>13.4432</v>
+      </c>
+      <c r="F51">
+        <v>15.5232</v>
+      </c>
+      <c r="G51">
+        <v>0.771</v>
+      </c>
+      <c r="H51">
+        <v>29.6</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0.867</v>
+      </c>
+      <c r="K51">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L51">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M51">
+        <v>3.70694016</v>
+      </c>
+      <c r="N51">
+        <v>-2.89594016</v>
+      </c>
+      <c r="O51">
+        <v>-0.6660662367999999</v>
+      </c>
+      <c r="P51">
+        <v>-2.2298739232</v>
+      </c>
+      <c r="Q51">
+        <v>-2.1738739232</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.3114337063020848</v>
+      </c>
+      <c r="T51">
+        <v>1.591343554328728</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.05031912897131849</v>
+      </c>
+      <c r="W51">
+        <v>0.2267837920016491</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.2187788216144282</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2719552482948714</v>
+      </c>
+      <c r="C52">
+        <v>4.108190230308519</v>
+      </c>
+      <c r="D52">
+        <v>19.17719023030852</v>
+      </c>
+      <c r="E52">
+        <v>13.76</v>
+      </c>
+      <c r="F52">
+        <v>15.84</v>
+      </c>
+      <c r="G52">
+        <v>0.771</v>
+      </c>
+      <c r="H52">
+        <v>29.6</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0.867</v>
+      </c>
+      <c r="K52">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L52">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M52">
+        <v>3.782592</v>
+      </c>
+      <c r="N52">
+        <v>-2.971592</v>
+      </c>
+      <c r="O52">
+        <v>-0.68346616</v>
+      </c>
+      <c r="P52">
+        <v>-2.28812584</v>
+      </c>
+      <c r="Q52">
+        <v>-2.23212584</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.3168863804281266</v>
+      </c>
+      <c r="T52">
+        <v>1.623170425415302</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.04931274639189212</v>
+      </c>
+      <c r="W52">
+        <v>0.2270241161616162</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.2144032451821396</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2739552482948714</v>
+      </c>
+      <c r="C53">
+        <v>3.628287851183547</v>
+      </c>
+      <c r="D53">
+        <v>19.01408785118355</v>
+      </c>
+      <c r="E53">
+        <v>14.0768</v>
+      </c>
+      <c r="F53">
+        <v>16.1568</v>
+      </c>
+      <c r="G53">
+        <v>0.771</v>
+      </c>
+      <c r="H53">
+        <v>29.6</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0.867</v>
+      </c>
+      <c r="K53">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L53">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M53">
+        <v>3.858243840000001</v>
+      </c>
+      <c r="N53">
+        <v>-3.047243840000001</v>
+      </c>
+      <c r="O53">
+        <v>-0.7008660832000001</v>
+      </c>
+      <c r="P53">
+        <v>-2.3463777568</v>
+      </c>
+      <c r="Q53">
+        <v>-2.2903777568</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.3225616126817618</v>
+      </c>
+      <c r="T53">
+        <v>1.656296352464594</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.04834582979597266</v>
+      </c>
+      <c r="W53">
+        <v>0.2272550158447217</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.2101992599824898</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2759552482948714</v>
+      </c>
+      <c r="C54">
+        <v>3.15113645278192</v>
+      </c>
+      <c r="D54">
+        <v>18.85373645278192</v>
+      </c>
+      <c r="E54">
+        <v>14.3936</v>
+      </c>
+      <c r="F54">
+        <v>16.4736</v>
+      </c>
+      <c r="G54">
+        <v>0.771</v>
+      </c>
+      <c r="H54">
+        <v>29.6</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0.867</v>
+      </c>
+      <c r="K54">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L54">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M54">
+        <v>3.93389568</v>
+      </c>
+      <c r="N54">
+        <v>-3.122895680000001</v>
+      </c>
+      <c r="O54">
+        <v>-0.7182660064</v>
+      </c>
+      <c r="P54">
+        <v>-2.404629673600001</v>
+      </c>
+      <c r="Q54">
+        <v>-2.348629673600001</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.3284733129459652</v>
+      </c>
+      <c r="T54">
+        <v>1.690802526474273</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.04741610229989626</v>
+      </c>
+      <c r="W54">
+        <v>0.2274770347707848</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.2061569665212881</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2779552482948713</v>
+      </c>
+      <c r="C55">
+        <v>2.67666701765804</v>
+      </c>
+      <c r="D55">
+        <v>18.69606701765804</v>
+      </c>
+      <c r="E55">
+        <v>14.7104</v>
+      </c>
+      <c r="F55">
+        <v>16.7904</v>
+      </c>
+      <c r="G55">
+        <v>0.771</v>
+      </c>
+      <c r="H55">
+        <v>29.6</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0.867</v>
+      </c>
+      <c r="K55">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L55">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M55">
+        <v>4.009547520000001</v>
+      </c>
+      <c r="N55">
+        <v>-3.198547520000001</v>
+      </c>
+      <c r="O55">
+        <v>-0.7356659296000001</v>
+      </c>
+      <c r="P55">
+        <v>-2.462881590400001</v>
+      </c>
+      <c r="Q55">
+        <v>-2.406881590400001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.3346365749235389</v>
+      </c>
+      <c r="T55">
+        <v>1.726777048314151</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.04652145886027557</v>
+      </c>
+      <c r="W55">
+        <v>0.2276906756241662</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.2022672124359808</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2799552482948714</v>
+      </c>
+      <c r="C56">
+        <v>2.204812817926939</v>
+      </c>
+      <c r="D56">
+        <v>18.54101281792694</v>
+      </c>
+      <c r="E56">
+        <v>15.0272</v>
+      </c>
+      <c r="F56">
+        <v>17.1072</v>
+      </c>
+      <c r="G56">
+        <v>0.771</v>
+      </c>
+      <c r="H56">
+        <v>29.6</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0.867</v>
+      </c>
+      <c r="K56">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L56">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M56">
+        <v>4.085199360000001</v>
+      </c>
+      <c r="N56">
+        <v>-3.274199360000001</v>
+      </c>
+      <c r="O56">
+        <v>-0.7530658528000002</v>
+      </c>
+      <c r="P56">
+        <v>-2.521133507200001</v>
+      </c>
+      <c r="Q56">
+        <v>-2.4651335072</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.3410678048131811</v>
+      </c>
+      <c r="T56">
+        <v>1.764315679799242</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.04565995036286306</v>
+      </c>
+      <c r="W56">
+        <v>0.2278964038533483</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.198521523316796</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2819552482948713</v>
+      </c>
+      <c r="C57">
+        <v>1.735509321103855</v>
+      </c>
+      <c r="D57">
+        <v>18.38850932110385</v>
+      </c>
+      <c r="E57">
+        <v>15.344</v>
+      </c>
+      <c r="F57">
+        <v>17.424</v>
+      </c>
+      <c r="G57">
+        <v>0.771</v>
+      </c>
+      <c r="H57">
+        <v>29.6</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0.867</v>
+      </c>
+      <c r="K57">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L57">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M57">
+        <v>4.1608512</v>
+      </c>
+      <c r="N57">
+        <v>-3.3498512</v>
+      </c>
+      <c r="O57">
+        <v>-0.7704657759999999</v>
+      </c>
+      <c r="P57">
+        <v>-2.579385424</v>
+      </c>
+      <c r="Q57">
+        <v>-2.523385424</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.3477848671423628</v>
+      </c>
+      <c r="T57">
+        <v>1.803522694905891</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.04482976944717466</v>
+      </c>
+      <c r="W57">
+        <v>0.2280946510560147</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.1949120410746724</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2839552482948714</v>
+      </c>
+      <c r="C58">
+        <v>1.268694100552782</v>
+      </c>
+      <c r="D58">
+        <v>18.23849410055278</v>
+      </c>
+      <c r="E58">
+        <v>15.6608</v>
+      </c>
+      <c r="F58">
+        <v>17.7408</v>
+      </c>
+      <c r="G58">
+        <v>0.771</v>
+      </c>
+      <c r="H58">
+        <v>29.6</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0.867</v>
+      </c>
+      <c r="K58">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L58">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M58">
+        <v>4.236503040000001</v>
+      </c>
+      <c r="N58">
+        <v>-3.425503040000001</v>
+      </c>
+      <c r="O58">
+        <v>-0.7878656992</v>
+      </c>
+      <c r="P58">
+        <v>-2.6376373408</v>
+      </c>
+      <c r="Q58">
+        <v>-2.5816373408</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.3548072504865075</v>
+      </c>
+      <c r="T58">
+        <v>1.844511847062844</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.04402923784990367</v>
+      </c>
+      <c r="W58">
+        <v>0.228285818001443</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.1914314689126246</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2859552482948714</v>
+      </c>
+      <c r="C59">
+        <v>0.8043067502830183</v>
+      </c>
+      <c r="D59">
+        <v>18.09090675028302</v>
+      </c>
+      <c r="E59">
+        <v>15.9776</v>
+      </c>
+      <c r="F59">
+        <v>18.0576</v>
+      </c>
+      <c r="G59">
+        <v>0.771</v>
+      </c>
+      <c r="H59">
+        <v>29.6</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0.867</v>
+      </c>
+      <c r="K59">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L59">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M59">
+        <v>4.31215488</v>
+      </c>
+      <c r="N59">
+        <v>-3.501154880000001</v>
+      </c>
+      <c r="O59">
+        <v>-0.8052656224000001</v>
+      </c>
+      <c r="P59">
+        <v>-2.6958892576</v>
+      </c>
+      <c r="Q59">
+        <v>-2.6398892576</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.3621562563117751</v>
+      </c>
+      <c r="T59">
+        <v>1.887407471413142</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.04325679508060712</v>
+      </c>
+      <c r="W59">
+        <v>0.228470277334751</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.1880730220895962</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2879552482948713</v>
+      </c>
+      <c r="C60">
+        <v>0.3422888038493035</v>
+      </c>
+      <c r="D60">
+        <v>17.9456888038493</v>
+      </c>
+      <c r="E60">
+        <v>16.2944</v>
+      </c>
+      <c r="F60">
+        <v>18.3744</v>
+      </c>
+      <c r="G60">
+        <v>0.771</v>
+      </c>
+      <c r="H60">
+        <v>29.6</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0.867</v>
+      </c>
+      <c r="K60">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L60">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M60">
+        <v>4.387806719999999</v>
+      </c>
+      <c r="N60">
+        <v>-3.57680672</v>
+      </c>
+      <c r="O60">
+        <v>-0.8226655455999998</v>
+      </c>
+      <c r="P60">
+        <v>-2.7541411744</v>
+      </c>
+      <c r="Q60">
+        <v>-2.6981411744</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.3698552147953887</v>
+      </c>
+      <c r="T60">
+        <v>1.932345744542026</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.04251098826887252</v>
+      </c>
+      <c r="W60">
+        <v>0.2286483760013932</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.1848303837777066</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2899552482948713</v>
+      </c>
+      <c r="C61">
+        <v>-0.1174163428731774</v>
+      </c>
+      <c r="D61">
+        <v>17.80278365712682</v>
+      </c>
+      <c r="E61">
+        <v>16.6112</v>
+      </c>
+      <c r="F61">
+        <v>18.6912</v>
+      </c>
+      <c r="G61">
+        <v>0.771</v>
+      </c>
+      <c r="H61">
+        <v>29.6</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0.867</v>
+      </c>
+      <c r="K61">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L61">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M61">
+        <v>4.46345856</v>
+      </c>
+      <c r="N61">
+        <v>-3.65245856</v>
+      </c>
+      <c r="O61">
+        <v>-0.8400654688</v>
+      </c>
+      <c r="P61">
+        <v>-2.812393091200001</v>
+      </c>
+      <c r="Q61">
+        <v>-2.756393091200001</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.3779297322294226</v>
+      </c>
+      <c r="T61">
+        <v>1.979476128555246</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.04179046304397637</v>
+      </c>
+      <c r="W61">
+        <v>0.2288204374250984</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.1816976654085929</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2919552482948714</v>
+      </c>
+      <c r="C62">
+        <v>-0.5748635052530844</v>
+      </c>
+      <c r="D62">
+        <v>17.66213649474691</v>
+      </c>
+      <c r="E62">
+        <v>16.928</v>
+      </c>
+      <c r="F62">
+        <v>19.008</v>
+      </c>
+      <c r="G62">
+        <v>0.771</v>
+      </c>
+      <c r="H62">
+        <v>29.6</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0.867</v>
+      </c>
+      <c r="K62">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L62">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M62">
+        <v>4.5391104</v>
+      </c>
+      <c r="N62">
+        <v>-3.7281104</v>
+      </c>
+      <c r="O62">
+        <v>-0.857465392</v>
+      </c>
+      <c r="P62">
+        <v>-2.870645008</v>
+      </c>
+      <c r="Q62">
+        <v>-2.814645008</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.3864079755351582</v>
+      </c>
+      <c r="T62">
+        <v>2.028963031769127</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.04109395532657676</v>
+      </c>
+      <c r="W62">
+        <v>0.2289867634680135</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.1786693709851164</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2939552482948714</v>
+      </c>
+      <c r="C63">
+        <v>-1.030105780007595</v>
+      </c>
+      <c r="D63">
+        <v>17.5236942199924</v>
+      </c>
+      <c r="E63">
+        <v>17.2448</v>
+      </c>
+      <c r="F63">
+        <v>19.3248</v>
+      </c>
+      <c r="G63">
+        <v>0.771</v>
+      </c>
+      <c r="H63">
+        <v>29.6</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0.867</v>
+      </c>
+      <c r="K63">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L63">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M63">
+        <v>4.61476224</v>
+      </c>
+      <c r="N63">
+        <v>-3.80376224</v>
+      </c>
+      <c r="O63">
+        <v>-0.8748653152</v>
+      </c>
+      <c r="P63">
+        <v>-2.9288969248</v>
+      </c>
+      <c r="Q63">
+        <v>-2.8728969248</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.3953210005488801</v>
+      </c>
+      <c r="T63">
+        <v>2.080987724891413</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.04042028392778043</v>
+      </c>
+      <c r="W63">
+        <v>0.229147636198046</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.1757403649033932</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2959552482948713</v>
+      </c>
+      <c r="C64">
+        <v>-1.483194612035618</v>
+      </c>
+      <c r="D64">
+        <v>17.38740538796438</v>
+      </c>
+      <c r="E64">
+        <v>17.5616</v>
+      </c>
+      <c r="F64">
+        <v>19.6416</v>
+      </c>
+      <c r="G64">
+        <v>0.771</v>
+      </c>
+      <c r="H64">
+        <v>29.6</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0.867</v>
+      </c>
+      <c r="K64">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L64">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M64">
+        <v>4.69041408</v>
+      </c>
+      <c r="N64">
+        <v>-3.87941408</v>
+      </c>
+      <c r="O64">
+        <v>-0.8922652383999999</v>
+      </c>
+      <c r="P64">
+        <v>-2.9871488416</v>
+      </c>
+      <c r="Q64">
+        <v>-2.9311488416</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.4047031321422717</v>
+      </c>
+      <c r="T64">
+        <v>2.135750559756976</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.03976834386442913</v>
+      </c>
+      <c r="W64">
+        <v>0.2293033194851743</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.1729058428888223</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2979552482948714</v>
+      </c>
+      <c r="C65">
+        <v>-1.934179858156362</v>
+      </c>
+      <c r="D65">
+        <v>17.25322014184364</v>
+      </c>
+      <c r="E65">
+        <v>17.8784</v>
+      </c>
+      <c r="F65">
+        <v>19.9584</v>
+      </c>
+      <c r="G65">
+        <v>0.771</v>
+      </c>
+      <c r="H65">
+        <v>29.6</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0.867</v>
+      </c>
+      <c r="K65">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L65">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M65">
+        <v>4.766065920000001</v>
+      </c>
+      <c r="N65">
+        <v>-3.955065920000001</v>
+      </c>
+      <c r="O65">
+        <v>-0.9096651616000001</v>
+      </c>
+      <c r="P65">
+        <v>-3.045400758400001</v>
+      </c>
+      <c r="Q65">
+        <v>-2.989400758400001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.4145924059839548</v>
+      </c>
+      <c r="T65">
+        <v>2.193473547858516</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.03913710031102548</v>
+      </c>
+      <c r="W65">
+        <v>0.2294540604457271</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.1701613057001108</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2999552482948714</v>
+      </c>
+      <c r="C66">
+        <v>-2.383109847919105</v>
+      </c>
+      <c r="D66">
+        <v>17.1210901520809</v>
+      </c>
+      <c r="E66">
+        <v>18.1952</v>
+      </c>
+      <c r="F66">
+        <v>20.2752</v>
+      </c>
+      <c r="G66">
+        <v>0.771</v>
+      </c>
+      <c r="H66">
+        <v>29.6</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0.867</v>
+      </c>
+      <c r="K66">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L66">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M66">
+        <v>4.841717760000001</v>
+      </c>
+      <c r="N66">
+        <v>-4.030717760000001</v>
+      </c>
+      <c r="O66">
+        <v>-0.9270650848000002</v>
+      </c>
+      <c r="P66">
+        <v>-3.103652675200001</v>
+      </c>
+      <c r="Q66">
+        <v>-3.047652675200001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.4250310839279536</v>
+      </c>
+      <c r="T66">
+        <v>2.254403368632365</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.03852558311866571</v>
+      </c>
+      <c r="W66">
+        <v>0.2296000907512626</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.1675025352985465</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.3019552482948714</v>
+      </c>
+      <c r="C67">
+        <v>-2.830031441640052</v>
+      </c>
+      <c r="D67">
+        <v>16.99096855835995</v>
+      </c>
+      <c r="E67">
+        <v>18.512</v>
+      </c>
+      <c r="F67">
+        <v>20.592</v>
+      </c>
+      <c r="G67">
+        <v>0.771</v>
+      </c>
+      <c r="H67">
+        <v>29.6</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0.867</v>
+      </c>
+      <c r="K67">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L67">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M67">
+        <v>4.9173696</v>
+      </c>
+      <c r="N67">
+        <v>-4.1063696</v>
+      </c>
+      <c r="O67">
+        <v>-0.9444650079999999</v>
+      </c>
+      <c r="P67">
+        <v>-3.161904592</v>
+      </c>
+      <c r="Q67">
+        <v>-3.105904592</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.4360662577544666</v>
+      </c>
+      <c r="T67">
+        <v>2.318814893450432</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.03793288183991702</v>
+      </c>
+      <c r="W67">
+        <v>0.2297416278166278</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.1649255732170305</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.3039552482948713</v>
+      </c>
+      <c r="C68">
+        <v>-3.274990085812647</v>
+      </c>
+      <c r="D68">
+        <v>16.86280991418735</v>
+      </c>
+      <c r="E68">
+        <v>18.8288</v>
+      </c>
+      <c r="F68">
+        <v>20.9088</v>
+      </c>
+      <c r="G68">
+        <v>0.771</v>
+      </c>
+      <c r="H68">
+        <v>29.6</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0.867</v>
+      </c>
+      <c r="K68">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L68">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M68">
+        <v>4.99302144</v>
+      </c>
+      <c r="N68">
+        <v>-4.18202144</v>
+      </c>
+      <c r="O68">
+        <v>-0.9618649311999998</v>
+      </c>
+      <c r="P68">
+        <v>-3.2201565088</v>
+      </c>
+      <c r="Q68">
+        <v>-3.1641565088</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.4477505594531273</v>
+      </c>
+      <c r="T68">
+        <v>2.387015331493092</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.03735814120597888</v>
+      </c>
+      <c r="W68">
+        <v>0.2298788758800122</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.1624267008955603</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.3059552482948714</v>
+      </c>
+      <c r="C69">
+        <v>-3.718029866028953</v>
+      </c>
+      <c r="D69">
+        <v>16.73657013397105</v>
+      </c>
+      <c r="E69">
+        <v>19.1456</v>
+      </c>
+      <c r="F69">
+        <v>21.2256</v>
+      </c>
+      <c r="G69">
+        <v>0.771</v>
+      </c>
+      <c r="H69">
+        <v>29.6</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0.867</v>
+      </c>
+      <c r="K69">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L69">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M69">
+        <v>5.068673280000001</v>
+      </c>
+      <c r="N69">
+        <v>-4.257673280000001</v>
+      </c>
+      <c r="O69">
+        <v>-0.9792648544000001</v>
+      </c>
+      <c r="P69">
+        <v>-3.2784084256</v>
+      </c>
+      <c r="Q69">
+        <v>-3.2224084256</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.4601430006486766</v>
+      </c>
+      <c r="T69">
+        <v>2.459349129417125</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.03680055700887471</v>
+      </c>
+      <c r="W69">
+        <v>0.2300120269862807</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.1600024217777162</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.3079552482948714</v>
+      </c>
+      <c r="C70">
+        <v>-4.15919355754156</v>
+      </c>
+      <c r="D70">
+        <v>16.61220644245844</v>
+      </c>
+      <c r="E70">
+        <v>19.4624</v>
+      </c>
+      <c r="F70">
+        <v>21.5424</v>
+      </c>
+      <c r="G70">
+        <v>0.771</v>
+      </c>
+      <c r="H70">
+        <v>29.6</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0.867</v>
+      </c>
+      <c r="K70">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L70">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M70">
+        <v>5.14432512</v>
+      </c>
+      <c r="N70">
+        <v>-4.33332512</v>
+      </c>
+      <c r="O70">
+        <v>-0.9966647776000001</v>
+      </c>
+      <c r="P70">
+        <v>-3.336660342400001</v>
+      </c>
+      <c r="Q70">
+        <v>-3.2806603424</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.4733099694189478</v>
+      </c>
+      <c r="T70">
+        <v>2.53620378971141</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.0362593723469795</v>
+      </c>
+      <c r="W70">
+        <v>0.2301412618835413</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.1576494449868674</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.3099552482948714</v>
+      </c>
+      <c r="C71">
+        <v>-4.598522673587976</v>
+      </c>
+      <c r="D71">
+        <v>16.48967732641202</v>
+      </c>
+      <c r="E71">
+        <v>19.7792</v>
+      </c>
+      <c r="F71">
+        <v>21.8592</v>
+      </c>
+      <c r="G71">
+        <v>0.771</v>
+      </c>
+      <c r="H71">
+        <v>29.6</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0.867</v>
+      </c>
+      <c r="K71">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L71">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M71">
+        <v>5.21997696</v>
+      </c>
+      <c r="N71">
+        <v>-4.40897696</v>
+      </c>
+      <c r="O71">
+        <v>-1.0140647008</v>
+      </c>
+      <c r="P71">
+        <v>-3.3949122592</v>
+      </c>
+      <c r="Q71">
+        <v>-3.3389122592</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.4873264200453655</v>
+      </c>
+      <c r="T71">
+        <v>2.618016815185972</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.03573387419702327</v>
+      </c>
+      <c r="W71">
+        <v>0.2302667508417509</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.1553646704218403</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.3119552482948714</v>
+      </c>
+      <c r="C72">
+        <v>-5.036057511591981</v>
+      </c>
+      <c r="D72">
+        <v>16.36894248840802</v>
+      </c>
+      <c r="E72">
+        <v>20.096</v>
+      </c>
+      <c r="F72">
+        <v>22.176</v>
+      </c>
+      <c r="G72">
+        <v>0.771</v>
+      </c>
+      <c r="H72">
+        <v>29.6</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0.867</v>
+      </c>
+      <c r="K72">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L72">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M72">
+        <v>5.295628800000001</v>
+      </c>
+      <c r="N72">
+        <v>-4.484628800000001</v>
+      </c>
+      <c r="O72">
+        <v>-1.031464624</v>
+      </c>
+      <c r="P72">
+        <v>-3.453164176000001</v>
+      </c>
+      <c r="Q72">
+        <v>-3.397164176000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.5022773007135444</v>
+      </c>
+      <c r="T72">
+        <v>2.705284042358837</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.03522339027992293</v>
+      </c>
+      <c r="W72">
+        <v>0.2303886544011544</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.1531451751300997</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.3139552482948714</v>
+      </c>
+      <c r="C73">
+        <v>-5.471837197350077</v>
+      </c>
+      <c r="D73">
+        <v>16.24996280264992</v>
+      </c>
+      <c r="E73">
+        <v>20.4128</v>
+      </c>
+      <c r="F73">
+        <v>22.4928</v>
+      </c>
+      <c r="G73">
+        <v>0.771</v>
+      </c>
+      <c r="H73">
+        <v>29.6</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0.867</v>
+      </c>
+      <c r="K73">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L73">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M73">
+        <v>5.37128064</v>
+      </c>
+      <c r="N73">
+        <v>-4.56028064</v>
+      </c>
+      <c r="O73">
+        <v>-1.0488645472</v>
+      </c>
+      <c r="P73">
+        <v>-3.5114160928</v>
+      </c>
+      <c r="Q73">
+        <v>-3.4554160928</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.5182592766002182</v>
+      </c>
+      <c r="T73">
+        <v>2.7985696989919</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.03472728619147333</v>
+      </c>
+      <c r="W73">
+        <v>0.2305071240574762</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.1509882008324926</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.3159552482948714</v>
+      </c>
+      <c r="C74">
+        <v>-5.905899727304849</v>
+      </c>
+      <c r="D74">
+        <v>16.13270027269515</v>
+      </c>
+      <c r="E74">
+        <v>20.7296</v>
+      </c>
+      <c r="F74">
+        <v>22.8096</v>
+      </c>
+      <c r="G74">
+        <v>0.771</v>
+      </c>
+      <c r="H74">
+        <v>29.6</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0.867</v>
+      </c>
+      <c r="K74">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L74">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M74">
+        <v>5.44693248</v>
+      </c>
+      <c r="N74">
+        <v>-4.63593248</v>
+      </c>
+      <c r="O74">
+        <v>-1.0662644704</v>
+      </c>
+      <c r="P74">
+        <v>-3.5696680096</v>
+      </c>
+      <c r="Q74">
+        <v>-3.5136680096</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.5353828221930832</v>
+      </c>
+      <c r="T74">
+        <v>2.898518616813039</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.03424496277214731</v>
+      </c>
+      <c r="W74">
+        <v>0.2306223028900112</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.1488911424875969</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.3179552482948713</v>
+      </c>
+      <c r="C75">
+        <v>-6.338282009001041</v>
+      </c>
+      <c r="D75">
+        <v>16.01711799099896</v>
+      </c>
+      <c r="E75">
+        <v>21.0464</v>
+      </c>
+      <c r="F75">
+        <v>23.1264</v>
+      </c>
+      <c r="G75">
+        <v>0.771</v>
+      </c>
+      <c r="H75">
+        <v>29.6</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0.867</v>
+      </c>
+      <c r="K75">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L75">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M75">
+        <v>5.52258432</v>
+      </c>
+      <c r="N75">
+        <v>-4.71158432</v>
+      </c>
+      <c r="O75">
+        <v>-1.0836643936</v>
+      </c>
+      <c r="P75">
+        <v>-3.6279199264</v>
+      </c>
+      <c r="Q75">
+        <v>-3.5719199264</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.5537747785706046</v>
+      </c>
+      <c r="T75">
+        <v>3.005871158176485</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.0337758536930768</v>
+      </c>
+      <c r="W75">
+        <v>0.2307343261380933</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.146851537795986</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.3199552482948713</v>
+      </c>
+      <c r="C76">
+        <v>-6.769019899815024</v>
+      </c>
+      <c r="D76">
+        <v>15.90318010018498</v>
+      </c>
+      <c r="E76">
+        <v>21.3632</v>
+      </c>
+      <c r="F76">
+        <v>23.4432</v>
+      </c>
+      <c r="G76">
+        <v>0.771</v>
+      </c>
+      <c r="H76">
+        <v>29.6</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0.867</v>
+      </c>
+      <c r="K76">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L76">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M76">
+        <v>5.598236160000001</v>
+      </c>
+      <c r="N76">
+        <v>-4.787236160000001</v>
+      </c>
+      <c r="O76">
+        <v>-1.1010643168</v>
+      </c>
+      <c r="P76">
+        <v>-3.686171843200001</v>
+      </c>
+      <c r="Q76">
+        <v>-3.630171843200001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.5735815008233203</v>
+      </c>
+      <c r="T76">
+        <v>3.121481587337119</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.03331942323776494</v>
+      </c>
+      <c r="W76">
+        <v>0.2308433217308218</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.1448670575554998</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.3219552482948713</v>
+      </c>
+      <c r="C77">
+        <v>-7.198148244042805</v>
+      </c>
+      <c r="D77">
+        <v>15.79085175595719</v>
+      </c>
+      <c r="E77">
+        <v>21.68</v>
+      </c>
+      <c r="F77">
+        <v>23.76</v>
+      </c>
+      <c r="G77">
+        <v>0.771</v>
+      </c>
+      <c r="H77">
+        <v>29.6</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0.867</v>
+      </c>
+      <c r="K77">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L77">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M77">
+        <v>5.673888</v>
+      </c>
+      <c r="N77">
+        <v>-4.862888</v>
+      </c>
+      <c r="O77">
+        <v>-1.11846424</v>
+      </c>
+      <c r="P77">
+        <v>-3.74442376</v>
+      </c>
+      <c r="Q77">
+        <v>-3.68842376</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.5949727608562529</v>
+      </c>
+      <c r="T77">
+        <v>3.246340850830604</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.03287516426126141</v>
+      </c>
+      <c r="W77">
+        <v>0.2309494107744108</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.1429354967880931</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.3239552482948714</v>
+      </c>
+      <c r="C78">
+        <v>-7.625700908427426</v>
+      </c>
+      <c r="D78">
+        <v>15.68009909157257</v>
+      </c>
+      <c r="E78">
+        <v>21.9968</v>
+      </c>
+      <c r="F78">
+        <v>24.0768</v>
+      </c>
+      <c r="G78">
+        <v>0.771</v>
+      </c>
+      <c r="H78">
+        <v>29.6</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0.867</v>
+      </c>
+      <c r="K78">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L78">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M78">
+        <v>5.74953984</v>
+      </c>
+      <c r="N78">
+        <v>-4.93853984</v>
+      </c>
+      <c r="O78">
+        <v>-1.1358641632</v>
+      </c>
+      <c r="P78">
+        <v>-3.8026756768</v>
+      </c>
+      <c r="Q78">
+        <v>-3.7466756768</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.6181466258919304</v>
+      </c>
+      <c r="T78">
+        <v>3.381605052948546</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.03244259631045534</v>
+      </c>
+      <c r="W78">
+        <v>0.2310527080010633</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.1410547665671972</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.3259552482948714</v>
+      </c>
+      <c r="C79">
+        <v>-8.051710816201577</v>
+      </c>
+      <c r="D79">
+        <v>15.57088918379842</v>
+      </c>
+      <c r="E79">
+        <v>22.3136</v>
+      </c>
+      <c r="F79">
+        <v>24.3936</v>
+      </c>
+      <c r="G79">
+        <v>0.771</v>
+      </c>
+      <c r="H79">
+        <v>29.6</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0.867</v>
+      </c>
+      <c r="K79">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L79">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M79">
+        <v>5.825191680000001</v>
+      </c>
+      <c r="N79">
+        <v>-5.014191680000001</v>
+      </c>
+      <c r="O79">
+        <v>-1.1532640864</v>
+      </c>
+      <c r="P79">
+        <v>-3.8609275936</v>
+      </c>
+      <c r="Q79">
+        <v>-3.8049275936</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.6433356096263623</v>
+      </c>
+      <c r="T79">
+        <v>3.528631359598483</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.03202126389083904</v>
+      </c>
+      <c r="W79">
+        <v>0.2311533221828677</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.1392228864819088</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.3279552482948714</v>
+      </c>
+      <c r="C80">
+        <v>-8.476209979717499</v>
+      </c>
+      <c r="D80">
+        <v>15.4631900202825</v>
+      </c>
+      <c r="E80">
+        <v>22.6304</v>
+      </c>
+      <c r="F80">
+        <v>24.7104</v>
+      </c>
+      <c r="G80">
+        <v>0.771</v>
+      </c>
+      <c r="H80">
+        <v>29.6</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0.867</v>
+      </c>
+      <c r="K80">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L80">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M80">
+        <v>5.90084352</v>
+      </c>
+      <c r="N80">
+        <v>-5.089843520000001</v>
+      </c>
+      <c r="O80">
+        <v>-1.1706640096</v>
+      </c>
+      <c r="P80">
+        <v>-3.9191795104</v>
+      </c>
+      <c r="Q80">
+        <v>-3.8631795104</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.6708145009730151</v>
+      </c>
+      <c r="T80">
+        <v>3.689023694125687</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.03161073486659751</v>
+      </c>
+      <c r="W80">
+        <v>0.2312513565138565</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.1374379776808587</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.3299552482948713</v>
+      </c>
+      <c r="C81">
+        <v>-8.899229531732043</v>
+      </c>
+      <c r="D81">
+        <v>15.35697046826796</v>
+      </c>
+      <c r="E81">
+        <v>22.9472</v>
+      </c>
+      <c r="F81">
+        <v>25.0272</v>
+      </c>
+      <c r="G81">
+        <v>0.771</v>
+      </c>
+      <c r="H81">
+        <v>29.6</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0.867</v>
+      </c>
+      <c r="K81">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L81">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M81">
+        <v>5.97649536</v>
+      </c>
+      <c r="N81">
+        <v>-5.16549536</v>
+      </c>
+      <c r="O81">
+        <v>-1.1880639328</v>
+      </c>
+      <c r="P81">
+        <v>-3.9774314272</v>
+      </c>
+      <c r="Q81">
+        <v>-3.9214314272</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.7009104295907775</v>
+      </c>
+      <c r="T81">
+        <v>3.864691489084053</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.0312105989822102</v>
+      </c>
+      <c r="W81">
+        <v>0.2313469089630482</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.1356982564443922</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.3319552482948714</v>
+      </c>
+      <c r="C82">
+        <v>-9.32079975541108</v>
+      </c>
+      <c r="D82">
+        <v>15.25220024458892</v>
+      </c>
+      <c r="E82">
+        <v>23.264</v>
+      </c>
+      <c r="F82">
+        <v>25.344</v>
+      </c>
+      <c r="G82">
+        <v>0.771</v>
+      </c>
+      <c r="H82">
+        <v>29.6</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0.867</v>
+      </c>
+      <c r="K82">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L82">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M82">
+        <v>6.0521472</v>
+      </c>
+      <c r="N82">
+        <v>-5.2411472</v>
+      </c>
+      <c r="O82">
+        <v>-1.205463856</v>
+      </c>
+      <c r="P82">
+        <v>-4.035683344000001</v>
+      </c>
+      <c r="Q82">
+        <v>-3.979683344000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.7340159510703166</v>
+      </c>
+      <c r="T82">
+        <v>4.057926063538257</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.03082046649493257</v>
+      </c>
+      <c r="W82">
+        <v>0.2314400726010101</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.1340020282388372</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.3339552482948713</v>
+      </c>
+      <c r="C83">
+        <v>-9.740950113114023</v>
+      </c>
+      <c r="D83">
+        <v>15.14884988688598</v>
+      </c>
+      <c r="E83">
+        <v>23.5808</v>
+      </c>
+      <c r="F83">
+        <v>25.6608</v>
+      </c>
+      <c r="G83">
+        <v>0.771</v>
+      </c>
+      <c r="H83">
+        <v>29.6</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0.867</v>
+      </c>
+      <c r="K83">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L83">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M83">
+        <v>6.127799040000001</v>
+      </c>
+      <c r="N83">
+        <v>-5.316799040000001</v>
+      </c>
+      <c r="O83">
+        <v>-1.2228637792</v>
+      </c>
+      <c r="P83">
+        <v>-4.093935260800001</v>
+      </c>
+      <c r="Q83">
+        <v>-4.037935260800001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.7706062642845437</v>
+      </c>
+      <c r="T83">
+        <v>4.271501119513954</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.03043996690857538</v>
+      </c>
+      <c r="W83">
+        <v>0.2315309359022322</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1323476822111973</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.3359552482948713</v>
+      </c>
+      <c r="C84">
+        <v>-10.15970927401603</v>
+      </c>
+      <c r="D84">
+        <v>15.04689072598397</v>
+      </c>
+      <c r="E84">
+        <v>23.8976</v>
+      </c>
+      <c r="F84">
+        <v>25.9776</v>
+      </c>
+      <c r="G84">
+        <v>0.771</v>
+      </c>
+      <c r="H84">
+        <v>29.6</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0.867</v>
+      </c>
+      <c r="K84">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L84">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M84">
+        <v>6.203450880000001</v>
+      </c>
+      <c r="N84">
+        <v>-5.392450880000001</v>
+      </c>
+      <c r="O84">
+        <v>-1.2402637024</v>
+      </c>
+      <c r="P84">
+        <v>-4.152187177600001</v>
+      </c>
+      <c r="Q84">
+        <v>-4.096187177600001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.8112621678559073</v>
+      </c>
+      <c r="T84">
+        <v>4.508806737264729</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.03006874779993422</v>
+      </c>
+      <c r="W84">
+        <v>0.2316195830253757</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.1307336860866705</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.3379552482948714</v>
+      </c>
+      <c r="C85">
+        <v>-10.57710514062207</v>
+      </c>
+      <c r="D85">
+        <v>14.94629485937793</v>
+      </c>
+      <c r="E85">
+        <v>24.2144</v>
+      </c>
+      <c r="F85">
+        <v>26.2944</v>
+      </c>
+      <c r="G85">
+        <v>0.771</v>
+      </c>
+      <c r="H85">
+        <v>29.6</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0.867</v>
+      </c>
+      <c r="K85">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L85">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M85">
+        <v>6.279102720000001</v>
+      </c>
+      <c r="N85">
+        <v>-5.468102720000001</v>
+      </c>
+      <c r="O85">
+        <v>-1.2576636256</v>
+      </c>
+      <c r="P85">
+        <v>-4.210439094400001</v>
+      </c>
+      <c r="Q85">
+        <v>-4.154439094400001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.856701118906255</v>
+      </c>
+      <c r="T85">
+        <v>4.774030662986185</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.02970647373005549</v>
+      </c>
+      <c r="W85">
+        <v>0.2317060940732628</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1291585814350239</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.3399552482948714</v>
+      </c>
+      <c r="C86">
+        <v>-10.99316487422461</v>
+      </c>
+      <c r="D86">
+        <v>14.84703512577539</v>
+      </c>
+      <c r="E86">
+        <v>24.5312</v>
+      </c>
+      <c r="F86">
+        <v>26.6112</v>
+      </c>
+      <c r="G86">
+        <v>0.771</v>
+      </c>
+      <c r="H86">
+        <v>29.6</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0.867</v>
+      </c>
+      <c r="K86">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L86">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M86">
+        <v>6.35475456</v>
+      </c>
+      <c r="N86">
+        <v>-5.54375456</v>
+      </c>
+      <c r="O86">
+        <v>-1.2750635488</v>
+      </c>
+      <c r="P86">
+        <v>-4.2686910112</v>
+      </c>
+      <c r="Q86">
+        <v>-4.2126910112</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.9078199388378954</v>
+      </c>
+      <c r="T86">
+        <v>5.072407579422818</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.02935282523326912</v>
+      </c>
+      <c r="W86">
+        <v>0.2317905453342954</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.1276209792750831</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.3419552482948713</v>
+      </c>
+      <c r="C87">
+        <v>-11.40791491935353</v>
+      </c>
+      <c r="D87">
+        <v>14.74908508064647</v>
+      </c>
+      <c r="E87">
+        <v>24.848</v>
+      </c>
+      <c r="F87">
+        <v>26.928</v>
+      </c>
+      <c r="G87">
+        <v>0.771</v>
+      </c>
+      <c r="H87">
+        <v>29.6</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0.867</v>
+      </c>
+      <c r="K87">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L87">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M87">
+        <v>6.430406400000001</v>
+      </c>
+      <c r="N87">
+        <v>-5.619406400000001</v>
+      </c>
+      <c r="O87">
+        <v>-1.292463472</v>
+      </c>
+      <c r="P87">
+        <v>-4.326942928000001</v>
+      </c>
+      <c r="Q87">
+        <v>-4.270942928000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.9657546014270886</v>
+      </c>
+      <c r="T87">
+        <v>5.410568084717673</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.02900749787758359</v>
+      </c>
+      <c r="W87">
+        <v>0.231873009506833</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.1261195559894939</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.3439552482948714</v>
+      </c>
+      <c r="C88">
+        <v>-11.82138102726457</v>
+      </c>
+      <c r="D88">
+        <v>14.65241897273543</v>
+      </c>
+      <c r="E88">
+        <v>25.1648</v>
+      </c>
+      <c r="F88">
+        <v>27.2448</v>
+      </c>
+      <c r="G88">
+        <v>0.771</v>
+      </c>
+      <c r="H88">
+        <v>29.6</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0.867</v>
+      </c>
+      <c r="K88">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L88">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M88">
+        <v>6.50605824</v>
+      </c>
+      <c r="N88">
+        <v>-5.69505824</v>
+      </c>
+      <c r="O88">
+        <v>-1.3098633952</v>
+      </c>
+      <c r="P88">
+        <v>-4.3851948448</v>
+      </c>
+      <c r="Q88">
+        <v>-4.3291948448</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>1.031965644386166</v>
+      </c>
+      <c r="T88">
+        <v>5.797037233626079</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.02867020139063495</v>
+      </c>
+      <c r="W88">
+        <v>0.2319535559079164</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.1246530495244998</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3459552482948713</v>
+      </c>
+      <c r="C89">
+        <v>-12.23358827851016</v>
+      </c>
+      <c r="D89">
+        <v>14.55701172148984</v>
+      </c>
+      <c r="E89">
+        <v>25.4816</v>
+      </c>
+      <c r="F89">
+        <v>27.5616</v>
+      </c>
+      <c r="G89">
+        <v>0.771</v>
+      </c>
+      <c r="H89">
+        <v>29.6</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0.867</v>
+      </c>
+      <c r="K89">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L89">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M89">
+        <v>6.58171008</v>
+      </c>
+      <c r="N89">
+        <v>-5.77071008</v>
+      </c>
+      <c r="O89">
+        <v>-1.3272633184</v>
+      </c>
+      <c r="P89">
+        <v>-4.4434467616</v>
+      </c>
+      <c r="Q89">
+        <v>-4.3874467616</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>1.10836300164664</v>
+      </c>
+      <c r="T89">
+        <v>6.242963174674238</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.02834065884591501</v>
+      </c>
+      <c r="W89">
+        <v>0.2320322506675955</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.1232202558518044</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3479552482948714</v>
+      </c>
+      <c r="C90">
+        <v>-12.64456110463411</v>
+      </c>
+      <c r="D90">
+        <v>14.46283889536589</v>
+      </c>
+      <c r="E90">
+        <v>25.7984</v>
+      </c>
+      <c r="F90">
+        <v>27.8784</v>
+      </c>
+      <c r="G90">
+        <v>0.771</v>
+      </c>
+      <c r="H90">
+        <v>29.6</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0.867</v>
+      </c>
+      <c r="K90">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L90">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M90">
+        <v>6.65736192</v>
+      </c>
+      <c r="N90">
+        <v>-5.846361920000001</v>
+      </c>
+      <c r="O90">
+        <v>-1.3446632416</v>
+      </c>
+      <c r="P90">
+        <v>-4.5016986784</v>
+      </c>
+      <c r="Q90">
+        <v>-4.4456986784</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>1.197493251783861</v>
+      </c>
+      <c r="T90">
+        <v>6.763210105897093</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.02801860590448416</v>
+      </c>
+      <c r="W90">
+        <v>0.2321091569100092</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.1218200256716703</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3499552482948713</v>
+      </c>
+      <c r="C91">
+        <v>-13.05432330902965</v>
+      </c>
+      <c r="D91">
+        <v>14.36987669097035</v>
+      </c>
+      <c r="E91">
+        <v>26.1152</v>
+      </c>
+      <c r="F91">
+        <v>28.1952</v>
+      </c>
+      <c r="G91">
+        <v>0.771</v>
+      </c>
+      <c r="H91">
+        <v>29.6</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0.867</v>
+      </c>
+      <c r="K91">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L91">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M91">
+        <v>6.73301376</v>
+      </c>
+      <c r="N91">
+        <v>-5.92201376</v>
+      </c>
+      <c r="O91">
+        <v>-1.3620631648</v>
+      </c>
+      <c r="P91">
+        <v>-4.5599505952</v>
+      </c>
+      <c r="Q91">
+        <v>-4.5039505952</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>1.30282900194603</v>
+      </c>
+      <c r="T91">
+        <v>7.378047388251375</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.02770379010780456</v>
+      </c>
+      <c r="W91">
+        <v>0.2321843349222563</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.1204512613382807</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3519552482948713</v>
+      </c>
+      <c r="C92">
+        <v>-13.46289808699817</v>
+      </c>
+      <c r="D92">
+        <v>14.27810191300182</v>
+      </c>
+      <c r="E92">
+        <v>26.432</v>
+      </c>
+      <c r="F92">
+        <v>28.512</v>
+      </c>
+      <c r="G92">
+        <v>0.771</v>
+      </c>
+      <c r="H92">
+        <v>29.6</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0.867</v>
+      </c>
+      <c r="K92">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L92">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M92">
+        <v>6.8086656</v>
+      </c>
+      <c r="N92">
+        <v>-5.9976656</v>
+      </c>
+      <c r="O92">
+        <v>-1.379463088</v>
+      </c>
+      <c r="P92">
+        <v>-4.618202512</v>
+      </c>
+      <c r="Q92">
+        <v>-4.562202512</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.429231902140633</v>
+      </c>
+      <c r="T92">
+        <v>8.115852127076513</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.02739597021771784</v>
+      </c>
+      <c r="W92">
+        <v>0.232257842312009</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.1191129139900776</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3539552482948713</v>
+      </c>
+      <c r="C93">
+        <v>-13.87030804504426</v>
+      </c>
+      <c r="D93">
+        <v>14.18749195495574</v>
+      </c>
+      <c r="E93">
+        <v>26.7488</v>
+      </c>
+      <c r="F93">
+        <v>28.8288</v>
+      </c>
+      <c r="G93">
+        <v>0.771</v>
+      </c>
+      <c r="H93">
+        <v>29.6</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0.867</v>
+      </c>
+      <c r="K93">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L93">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M93">
+        <v>6.88431744</v>
+      </c>
+      <c r="N93">
+        <v>-6.07331744</v>
+      </c>
+      <c r="O93">
+        <v>-1.3968630112</v>
+      </c>
+      <c r="P93">
+        <v>-4.676454428800001</v>
+      </c>
+      <c r="Q93">
+        <v>-4.6204544288</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.583724335711814</v>
+      </c>
+      <c r="T93">
+        <v>9.017613474529458</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.02709491559994072</v>
+      </c>
+      <c r="W93">
+        <v>0.2323297341547342</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1178039808693075</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3559552482948714</v>
+      </c>
+      <c r="C94">
+        <v>-14.27657521944061</v>
+      </c>
+      <c r="D94">
+        <v>14.0980247805594</v>
+      </c>
+      <c r="E94">
+        <v>27.0656</v>
+      </c>
+      <c r="F94">
+        <v>29.1456</v>
+      </c>
+      <c r="G94">
+        <v>0.771</v>
+      </c>
+      <c r="H94">
+        <v>29.6</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0.867</v>
+      </c>
+      <c r="K94">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L94">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M94">
+        <v>6.959969280000001</v>
+      </c>
+      <c r="N94">
+        <v>-6.148969280000001</v>
+      </c>
+      <c r="O94">
+        <v>-1.4142629344</v>
+      </c>
+      <c r="P94">
+        <v>-4.734706345600001</v>
+      </c>
+      <c r="Q94">
+        <v>-4.678706345600001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.776839877675792</v>
+      </c>
+      <c r="T94">
+        <v>10.14481515884564</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.02680040564776745</v>
+      </c>
+      <c r="W94">
+        <v>0.2324000631313131</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.1165235028163802</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3579552482948714</v>
+      </c>
+      <c r="C95">
+        <v>-14.6817210940949</v>
+      </c>
+      <c r="D95">
+        <v>14.0096789059051</v>
+      </c>
+      <c r="E95">
+        <v>27.3824</v>
+      </c>
+      <c r="F95">
+        <v>29.4624</v>
+      </c>
+      <c r="G95">
+        <v>0.771</v>
+      </c>
+      <c r="H95">
+        <v>29.6</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0.867</v>
+      </c>
+      <c r="K95">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L95">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M95">
+        <v>7.035621120000001</v>
+      </c>
+      <c r="N95">
+        <v>-6.224621120000001</v>
+      </c>
+      <c r="O95">
+        <v>-1.4316628576</v>
+      </c>
+      <c r="P95">
+        <v>-4.792958262400001</v>
+      </c>
+      <c r="Q95">
+        <v>-4.736958262400001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>2.025131288772334</v>
+      </c>
+      <c r="T95">
+        <v>11.59407446725217</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.02651222924295275</v>
+      </c>
+      <c r="W95">
+        <v>0.2324688796567829</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.1152705619258815</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3599552482948714</v>
+      </c>
+      <c r="C96">
+        <v>-15.0857666177492</v>
+      </c>
+      <c r="D96">
+        <v>13.92243338225081</v>
+      </c>
+      <c r="E96">
+        <v>27.6992</v>
+      </c>
+      <c r="F96">
+        <v>29.7792</v>
+      </c>
+      <c r="G96">
+        <v>0.771</v>
+      </c>
+      <c r="H96">
+        <v>29.6</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0.867</v>
+      </c>
+      <c r="K96">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L96">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M96">
+        <v>7.111272960000001</v>
+      </c>
+      <c r="N96">
+        <v>-6.300272960000001</v>
+      </c>
+      <c r="O96">
+        <v>-1.4490627808</v>
+      </c>
+      <c r="P96">
+        <v>-4.851210179200001</v>
+      </c>
+      <c r="Q96">
+        <v>-4.795210179200001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>2.356186503567724</v>
+      </c>
+      <c r="T96">
+        <v>13.5264202117942</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.02623018425100644</v>
+      </c>
+      <c r="W96">
+        <v>0.2325362320008597</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.114044279352202</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3619552482948714</v>
+      </c>
+      <c r="C97">
+        <v>-15.4887322205405</v>
+      </c>
+      <c r="D97">
+        <v>13.8362677794595</v>
+      </c>
+      <c r="E97">
+        <v>28.016</v>
+      </c>
+      <c r="F97">
+        <v>30.096</v>
+      </c>
+      <c r="G97">
+        <v>0.771</v>
+      </c>
+      <c r="H97">
+        <v>29.6</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0.867</v>
+      </c>
+      <c r="K97">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L97">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M97">
+        <v>7.186924800000001</v>
+      </c>
+      <c r="N97">
+        <v>-6.375924800000001</v>
+      </c>
+      <c r="O97">
+        <v>-1.466462704</v>
+      </c>
+      <c r="P97">
+        <v>-4.909462096</v>
+      </c>
+      <c r="Q97">
+        <v>-4.853462096</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>2.81966380428127</v>
+      </c>
+      <c r="T97">
+        <v>16.23170425415304</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.02595407704836427</v>
+      </c>
+      <c r="W97">
+        <v>0.2326021664008506</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1128438132537577</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3639552482948714</v>
+      </c>
+      <c r="C98">
+        <v>-15.89063782995026</v>
+      </c>
+      <c r="D98">
+        <v>13.75116217004974</v>
+      </c>
+      <c r="E98">
+        <v>28.3328</v>
+      </c>
+      <c r="F98">
+        <v>30.4128</v>
+      </c>
+      <c r="G98">
+        <v>0.771</v>
+      </c>
+      <c r="H98">
+        <v>29.6</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0.867</v>
+      </c>
+      <c r="K98">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L98">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M98">
+        <v>7.26257664</v>
+      </c>
+      <c r="N98">
+        <v>-6.45157664</v>
+      </c>
+      <c r="O98">
+        <v>-1.4838626272</v>
+      </c>
+      <c r="P98">
+        <v>-4.9677140128</v>
+      </c>
+      <c r="Q98">
+        <v>-4.9117140128</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>3.514879755351579</v>
+      </c>
+      <c r="T98">
+        <v>20.28963031769126</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.02568372207911048</v>
+      </c>
+      <c r="W98">
+        <v>0.2326667271675084</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1116683568656978</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3659552482948714</v>
+      </c>
+      <c r="C99">
+        <v>-16.2915028861688</v>
+      </c>
+      <c r="D99">
+        <v>13.66709711383119</v>
+      </c>
+      <c r="E99">
+        <v>28.6496</v>
+      </c>
+      <c r="F99">
+        <v>30.7296</v>
+      </c>
+      <c r="G99">
+        <v>0.771</v>
+      </c>
+      <c r="H99">
+        <v>29.6</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0.867</v>
+      </c>
+      <c r="K99">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L99">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M99">
+        <v>7.33822848</v>
+      </c>
+      <c r="N99">
+        <v>-6.52722848</v>
+      </c>
+      <c r="O99">
+        <v>-1.5012625504</v>
+      </c>
+      <c r="P99">
+        <v>-5.0259659296</v>
+      </c>
+      <c r="Q99">
+        <v>-4.9699659296</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>4.67357300713544</v>
+      </c>
+      <c r="T99">
+        <v>27.05284042358835</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.02541894143911965</v>
+      </c>
+      <c r="W99">
+        <v>0.2327299567843382</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1105171366918246</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3679552482948714</v>
+      </c>
+      <c r="C100">
+        <v>-16.6913463568996</v>
+      </c>
+      <c r="D100">
+        <v>13.5840536431004</v>
+      </c>
+      <c r="E100">
+        <v>28.9664</v>
+      </c>
+      <c r="F100">
+        <v>31.0464</v>
+      </c>
+      <c r="G100">
+        <v>0.771</v>
+      </c>
+      <c r="H100">
+        <v>29.6</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0.867</v>
+      </c>
+      <c r="K100">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L100">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M100">
+        <v>7.41388032</v>
+      </c>
+      <c r="N100">
+        <v>-6.60288032</v>
+      </c>
+      <c r="O100">
+        <v>-1.5186624736</v>
+      </c>
+      <c r="P100">
+        <v>-5.0842178464</v>
+      </c>
+      <c r="Q100">
+        <v>-5.0282178464</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>6.990959510703158</v>
+      </c>
+      <c r="T100">
+        <v>40.57926063538252</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.02515956448565924</v>
+      </c>
+      <c r="W100">
+        <v>0.2327918960008246</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1093894108072141</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3699552482948714</v>
+      </c>
+      <c r="C101">
+        <v>-17.09018675162712</v>
+      </c>
+      <c r="D101">
+        <v>13.50201324837288</v>
+      </c>
+      <c r="E101">
+        <v>29.2832</v>
+      </c>
+      <c r="F101">
+        <v>31.3632</v>
+      </c>
+      <c r="G101">
+        <v>0.771</v>
+      </c>
+      <c r="H101">
+        <v>29.6</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0.867</v>
+      </c>
+      <c r="K101">
+        <v>0.05599999999999994</v>
+      </c>
+      <c r="L101">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M101">
+        <v>7.48953216</v>
+      </c>
+      <c r="N101">
+        <v>-6.67853216</v>
+      </c>
+      <c r="O101">
+        <v>-1.5360623968</v>
+      </c>
+      <c r="P101">
+        <v>-5.1424697632</v>
+      </c>
+      <c r="Q101">
+        <v>-5.0864697632</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>13.94311902140632</v>
+      </c>
+      <c r="T101">
+        <v>81.15852127076504</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.02490542747065258</v>
+      </c>
+      <c r="W101">
+        <v>0.2328525839200082</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.1082844672637069</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
